--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI23"/>
+  <dimension ref="A1:BI26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46114.79166666666</v>
+        <v>46114.75</v>
       </c>
     </row>
     <row r="20">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46114.79166666666</v>
+        <v>46114.75</v>
       </c>
     </row>
     <row r="21">
@@ -4491,27 +4491,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46114.875</v>
+        <v>46114.79166666666</v>
       </c>
     </row>
     <row r="22">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.05</v>
+        <v>1.52</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.62</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.92</v>
+        <v>6.2</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46114.89583333334</v>
+        <v>46114.79166666666</v>
       </c>
     </row>
     <row r="23">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,141 +4938,732 @@
         </is>
       </c>
       <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" s="3" t="n">
+        <v>46114.875</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" s="3" t="n">
+        <v>46114.875</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
         <v>1.52</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q25" t="n">
         <v>4.12</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>6.68</v>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AF25" t="n">
         <v>2</v>
       </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI23" s="3" t="n">
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" s="3" t="n">
+        <v>46114.89583333334</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" s="3" t="n">
         <v>46114.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G16" t="n">

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI26"/>
+  <dimension ref="A1:BI29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5279,27 +5279,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>6.68</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46114.89583333334</v>
+        <v>46114.875</v>
       </c>
     </row>
     <row r="26">
@@ -5476,27 +5476,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,141 +5529,732 @@
         </is>
       </c>
       <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" s="3" t="n">
+        <v>46114.875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Greece Super League</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Panserraikos</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" s="3" t="n">
+        <v>46114.875</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
         <v>4.05</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q28" t="n">
         <v>3.62</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R28" t="n">
         <v>1.92</v>
       </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AF28" t="n">
         <v>1.85</v>
       </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI26" s="3" t="n">
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" s="3" t="n">
+        <v>46114.89583333334</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI29" s="3" t="n">
         <v>46114.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.07</v>
+        <v>1.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.52</v>
+        <v>3.07</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>4.05</v>
+        <v>1.52</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.62</v>
+        <v>4.12</v>
       </c>
       <c r="R28" t="n">
-        <v>1.92</v>
+        <v>6.68</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.52</v>
+        <v>4.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.12</v>
+        <v>3.62</v>
       </c>
       <c r="R29" t="n">
-        <v>6.68</v>
+        <v>1.92</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF29" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.52</v>
+        <v>3.07</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R21" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.07</v>
+        <v>1.52</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.52</v>
+        <v>4.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.12</v>
+        <v>3.62</v>
       </c>
       <c r="R28" t="n">
-        <v>6.68</v>
+        <v>1.92</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF28" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4.05</v>
+        <v>1.52</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.62</v>
+        <v>4.12</v>
       </c>
       <c r="R29" t="n">
-        <v>1.92</v>
+        <v>6.68</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.07</v>
+        <v>1.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.52</v>
+        <v>3.07</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>4.05</v>
+        <v>1.52</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.62</v>
+        <v>4.12</v>
       </c>
       <c r="R28" t="n">
-        <v>1.92</v>
+        <v>6.68</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.52</v>
+        <v>4.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.12</v>
+        <v>3.62</v>
       </c>
       <c r="R29" t="n">
-        <v>6.68</v>
+        <v>1.92</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF29" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G27" t="n">

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI29"/>
+  <dimension ref="A1:BI31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="BI8" s="3" t="n">
-        <v>46114.54166666666</v>
+        <v>46114.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
-        <v>46114.58333333334</v>
+        <v>46114.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46114.625</v>
+        <v>46114.55208333334</v>
       </c>
     </row>
     <row r="11">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.81</v>
+        <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="R11" t="n">
-        <v>2.58</v>
+        <v>3.89</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46114.625</v>
+        <v>46114.58333333334</v>
       </c>
     </row>
     <row r="12">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>2.81</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R12" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46114.65625</v>
+        <v>46114.625</v>
       </c>
     </row>
     <row r="13">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>4.32</v>
       </c>
       <c r="R13" t="n">
-        <v>3.65</v>
+        <v>4.32</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46114.66666666666</v>
+        <v>46114.625</v>
       </c>
     </row>
     <row r="14">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>3.83</v>
+        <v>3.45</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46114.6875</v>
+        <v>46114.65625</v>
       </c>
     </row>
     <row r="15">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46114.72916666666</v>
+        <v>46114.66666666666</v>
       </c>
     </row>
     <row r="16">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46114.72916666666</v>
+        <v>46114.6875</v>
       </c>
     </row>
     <row r="17">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46114.75</v>
+        <v>46114.72916666666</v>
       </c>
     </row>
     <row r="20">
@@ -4294,27 +4294,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46114.75</v>
+        <v>46114.72916666666</v>
       </c>
     </row>
     <row r="21">
@@ -4491,27 +4491,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46114.79166666666</v>
+        <v>46114.75</v>
       </c>
     </row>
     <row r="22">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46114.79166666666</v>
+        <v>46114.75</v>
       </c>
     </row>
     <row r="23">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4934,17 +4934,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46114.875</v>
+        <v>46114.79166666666</v>
       </c>
     </row>
     <row r="24">
@@ -5082,27 +5082,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46114.875</v>
+        <v>46114.79166666666</v>
       </c>
     </row>
     <row r="25">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5870,27 +5870,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>6.68</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46114.89583333334</v>
+        <v>46114.875</v>
       </c>
     </row>
     <row r="29">
@@ -6067,27 +6067,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,145 +6116,539 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI29" s="3" t="n">
+        <v>46114.875</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="P29" t="n">
+      <c r="P30" t="n">
         <v>4.05</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Q30" t="n">
         <v>3.62</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R30" t="n">
         <v>1.92</v>
       </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AF30" t="n">
         <v>1.85</v>
       </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI29" s="3" t="n">
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI30" s="3" t="n">
+        <v>46114.89583333334</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI31" s="3" t="n">
         <v>46114.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI31"/>
+  <dimension ref="A1:BI32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
-        <v>46114.54166666666</v>
+        <v>46114.5</v>
       </c>
     </row>
     <row r="10">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46114.55208333334</v>
+        <v>46114.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46114.58333333334</v>
+        <v>46114.55208333334</v>
       </c>
     </row>
     <row r="12">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.81</v>
+        <v>2.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="R12" t="n">
-        <v>2.58</v>
+        <v>3.89</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46114.625</v>
+        <v>46114.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46114.65625</v>
+        <v>46114.625</v>
       </c>
     </row>
     <row r="15">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46114.66666666666</v>
+        <v>46114.65625</v>
       </c>
     </row>
     <row r="16">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>3.83</v>
+        <v>3.65</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46114.6875</v>
+        <v>46114.66666666666</v>
       </c>
     </row>
     <row r="17">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46114.72916666666</v>
+        <v>46114.6875</v>
       </c>
     </row>
     <row r="18">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4491,27 +4491,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46114.75</v>
+        <v>46114.72916666666</v>
       </c>
     </row>
     <row r="22">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46114.79166666666</v>
+        <v>46114.75</v>
       </c>
     </row>
     <row r="24">
@@ -5279,27 +5279,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46114.875</v>
+        <v>46114.79166666666</v>
       </c>
     </row>
     <row r="26">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -6264,27 +6264,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,17 +6313,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46114.89583333334</v>
+        <v>46114.875</v>
       </c>
     </row>
     <row r="31">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,141 +6514,338 @@
         </is>
       </c>
       <c r="P31" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI31" s="3" t="n">
+        <v>46114.89583333334</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
         <v>1.52</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q32" t="n">
         <v>4.12</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R32" t="n">
         <v>6.68</v>
       </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AF32" t="n">
         <v>2</v>
       </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI31" s="3" t="n">
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI32" s="3" t="n">
         <v>46114.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.07</v>
+        <v>1.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.52</v>
+        <v>3.07</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.05</v>
+        <v>1.52</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.62</v>
+        <v>4.12</v>
       </c>
       <c r="R31" t="n">
-        <v>1.92</v>
+        <v>6.68</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.52</v>
+        <v>4.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.12</v>
+        <v>3.62</v>
       </c>
       <c r="R32" t="n">
-        <v>6.68</v>
+        <v>1.92</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.52</v>
+        <v>4.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.12</v>
+        <v>3.62</v>
       </c>
       <c r="R31" t="n">
-        <v>6.68</v>
+        <v>1.92</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>4.05</v>
+        <v>1.52</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.62</v>
+        <v>4.12</v>
       </c>
       <c r="R32" t="n">
-        <v>1.92</v>
+        <v>6.68</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.73</v>
+        <v>2.81</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.32</v>
+        <v>3.35</v>
       </c>
       <c r="R13" t="n">
-        <v>4.32</v>
+        <v>2.58</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.81</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>4.32</v>
       </c>
       <c r="R14" t="n">
-        <v>2.58</v>
+        <v>4.32</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P30" t="n">

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.52</v>
+        <v>3.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.07</v>
+        <v>1.52</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P30" t="n">

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.07</v>
+        <v>1.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.52</v>
+        <v>3.07</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.81</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.35</v>
+        <v>4.32</v>
       </c>
       <c r="R13" t="n">
-        <v>2.58</v>
+        <v>4.32</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>2.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.32</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>4.32</v>
+        <v>2.58</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.73</v>
+        <v>2.81</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.32</v>
+        <v>3.35</v>
       </c>
       <c r="R13" t="n">
-        <v>4.32</v>
+        <v>2.58</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.81</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>4.32</v>
       </c>
       <c r="R14" t="n">
-        <v>2.58</v>
+        <v>4.32</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.52</v>
+        <v>3.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.07</v>
+        <v>1.52</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.05</v>
+        <v>1.52</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.62</v>
+        <v>4.12</v>
       </c>
       <c r="R31" t="n">
-        <v>1.92</v>
+        <v>6.68</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.52</v>
+        <v>4.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.12</v>
+        <v>3.62</v>
       </c>
       <c r="R32" t="n">
-        <v>6.68</v>
+        <v>1.92</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.81</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.35</v>
+        <v>4.32</v>
       </c>
       <c r="R13" t="n">
-        <v>2.58</v>
+        <v>4.32</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>2.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.32</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>4.32</v>
+        <v>2.58</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.07</v>
+        <v>1.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.52</v>
+        <v>3.07</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P30" t="n">

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.52</v>
+        <v>3.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.07</v>
+        <v>1.52</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.52</v>
+        <v>4.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.12</v>
+        <v>3.62</v>
       </c>
       <c r="R31" t="n">
-        <v>6.68</v>
+        <v>1.92</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>4.05</v>
+        <v>1.52</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.62</v>
+        <v>4.12</v>
       </c>
       <c r="R32" t="n">
-        <v>1.92</v>
+        <v>6.68</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P30" t="n">

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P30" t="n">

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.73</v>
+        <v>2.81</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.32</v>
+        <v>3.35</v>
       </c>
       <c r="R13" t="n">
-        <v>4.32</v>
+        <v>2.58</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.81</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>4.32</v>
       </c>
       <c r="R14" t="n">
-        <v>2.58</v>
+        <v>4.32</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.93</v>
+        <v>2.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AG2" t="n">
         <v>1.92</v>
       </c>
       <c r="AH2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>1.84</v>
       </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.54</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
         <v>3.6</v>
       </c>
       <c r="R4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL4" t="n">
         <v>2.1</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
+      <c r="AM4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1.75</v>
       </c>
-      <c r="AF4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.07</v>
+        <v>1.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.52</v>
+        <v>3.07</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.05</v>
+        <v>1.52</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.62</v>
+        <v>4.12</v>
       </c>
       <c r="R31" t="n">
-        <v>1.92</v>
+        <v>6.68</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.52</v>
+        <v>4.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.12</v>
+        <v>3.62</v>
       </c>
       <c r="R32" t="n">
-        <v>6.68</v>
+        <v>1.92</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -2780,124 +2780,124 @@
         <v>3.89</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.81</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.35</v>
+        <v>4.32</v>
       </c>
       <c r="R13" t="n">
-        <v>2.58</v>
+        <v>4.32</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>2.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.32</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>4.32</v>
+        <v>2.58</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3371,124 +3371,124 @@
         <v>3.45</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.52</v>
+        <v>3.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.07</v>
+        <v>1.52</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.52</v>
+        <v>4.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.12</v>
+        <v>3.62</v>
       </c>
       <c r="R31" t="n">
-        <v>6.68</v>
+        <v>1.92</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>4.05</v>
+        <v>1.52</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.62</v>
+        <v>4.12</v>
       </c>
       <c r="R32" t="n">
-        <v>1.92</v>
+        <v>6.68</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.46</v>
+        <v>3.24</v>
       </c>
       <c r="R12" t="n">
-        <v>3.89</v>
+        <v>4.58</v>
       </c>
       <c r="S12" t="n">
         <v>2.55</v>
@@ -2798,7 +2798,7 @@
         <v>3.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
         <v>7.4</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.73</v>
+        <v>2.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.32</v>
+        <v>3.28</v>
       </c>
       <c r="R13" t="n">
-        <v>4.32</v>
+        <v>2.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.46</v>
+        <v>2.03</v>
       </c>
       <c r="U13" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="W13" t="n">
-        <v>3.66</v>
+        <v>2.65</v>
       </c>
       <c r="X13" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.75</v>
+        <v>7.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>5.25</v>
+        <v>2.99</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.52</v>
+        <v>2.09</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.55</v>
+        <v>1.74</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.18</v>
+        <v>4.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.85</v>
+        <v>8</v>
       </c>
       <c r="AJ13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY13" t="n">
         <v>1.2</v>
       </c>
-      <c r="AK13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.25</v>
+        <v>1.88</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.69</v>
+        <v>2.23</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.15</v>
+        <v>3.42</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.81</v>
+        <v>1.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>2.58</v>
+        <v>3.9</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.03</v>
+        <v>2.46</v>
       </c>
       <c r="U14" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
-        <v>2.65</v>
+        <v>3.66</v>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.1</v>
+        <v>4.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AC14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY14" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD14" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN14" t="n">
+      <c r="AZ14" t="n">
         <v>1.44</v>
       </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>2.17</v>
-      </c>
       <c r="BA14" t="n">
-        <v>1.88</v>
+        <v>3.25</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.23</v>
+        <v>1.69</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.42</v>
+        <v>5.15</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.07</v>
+        <v>1.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.52</v>
+        <v>3.07</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.05</v>
+        <v>1.52</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.62</v>
+        <v>4.12</v>
       </c>
       <c r="R31" t="n">
-        <v>1.92</v>
+        <v>6.68</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.52</v>
+        <v>4.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.12</v>
+        <v>3.62</v>
       </c>
       <c r="R32" t="n">
-        <v>6.68</v>
+        <v>1.92</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q24" t="n">
         <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R25" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.52</v>
+        <v>4.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.12</v>
+        <v>3.62</v>
       </c>
       <c r="R31" t="n">
-        <v>6.68</v>
+        <v>1.92</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>4.05</v>
+        <v>1.52</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.62</v>
+        <v>4.12</v>
       </c>
       <c r="R32" t="n">
-        <v>1.92</v>
+        <v>6.68</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
         <v>3.1</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.05</v>
+        <v>1.52</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.62</v>
+        <v>4.12</v>
       </c>
       <c r="R31" t="n">
-        <v>1.92</v>
+        <v>6.68</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.52</v>
+        <v>4.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.12</v>
+        <v>3.62</v>
       </c>
       <c r="R32" t="n">
-        <v>6.68</v>
+        <v>1.92</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="R2" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S2" t="n">
         <v>2.63</v>
@@ -822,7 +822,7 @@
         <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="X2" t="n">
         <v>1.92</v>
@@ -840,10 +840,10 @@
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>1.36</v>
@@ -852,67 +852,67 @@
         <v>3.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="AM2" t="n">
         <v>1.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="AS2" t="n">
         <v>1.66</v>
       </c>
       <c r="AT2" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="AX2" t="n">
         <v>2.06</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="BB2" t="n">
         <v>1.11</v>
@@ -924,10 +924,10 @@
         <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>4.58</v>
+        <v>4.4</v>
       </c>
       <c r="S12" t="n">
         <v>2.55</v>
@@ -2789,19 +2789,19 @@
         <v>4.35</v>
       </c>
       <c r="V12" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W12" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="X12" t="n">
         <v>3.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AA12" t="n">
         <v>1.03</v>
@@ -2810,25 +2810,25 @@
         <v>1.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AD12" t="n">
         <v>2.8</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
         <v>3.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AI12" t="n">
-        <v>6.9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.04</v>
@@ -2840,10 +2840,10 @@
         <v>1.77</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,16 +2885,16 @@
         <v>3</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="BF12" t="n">
         <v>1.12</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="T13" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="U13" t="n">
-        <v>3.2</v>
+        <v>4.14</v>
       </c>
       <c r="V13" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>2.65</v>
+        <v>3.42</v>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AB13" t="n">
         <v>1.02</v>
       </c>
       <c r="AC13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD13" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AQ13" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.88</v>
+        <v>3</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.23</v>
+        <v>1.76</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.42</v>
+        <v>4.85</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>3.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="R14" t="n">
-        <v>3.9</v>
+        <v>2.26</v>
       </c>
       <c r="S14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR14" t="n">
         <v>2.1</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="V14" t="n">
+      <c r="AS14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY14" t="n">
         <v>1.22</v>
       </c>
-      <c r="W14" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF14" t="n">
+      <c r="AZ14" t="n">
         <v>2.55</v>
       </c>
-      <c r="AG14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BA14" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.69</v>
+        <v>2.29</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.15</v>
+        <v>3.34</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="R17" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5198,7 +5198,7 @@
         <v>1.08</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL24" t="n">
         <v>1.82</v>
@@ -5249,7 +5249,7 @@
         <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC24" t="n">
         <v>2.04</v>
@@ -5261,7 +5261,7 @@
         <v>1.73</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5335,7 +5335,7 @@
         <v>2.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
         <v>2.45</v>
@@ -5371,10 +5371,10 @@
         <v>1.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="AE25" t="n">
         <v>2.19</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.52</v>
+        <v>4.37</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.12</v>
+        <v>3.37</v>
       </c>
       <c r="R31" t="n">
-        <v>6.68</v>
+        <v>1.86</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR31" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>4.05</v>
+        <v>1.53</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.62</v>
+        <v>4.33</v>
       </c>
       <c r="R32" t="n">
-        <v>1.92</v>
+        <v>5.95</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AE32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR32" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="T15" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="U15" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="V15" t="n">
         <v>1.37</v>
@@ -3386,28 +3386,28 @@
         <v>2.8</v>
       </c>
       <c r="X15" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="Z15" t="n">
         <v>7.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB15" t="n">
         <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="AF15" t="n">
         <v>1.72</v>
@@ -3416,13 +3416,13 @@
         <v>3.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AI15" t="n">
-        <v>6.25</v>
+        <v>7.38</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK15" t="n">
         <v>1.78</v>
@@ -3431,10 +3431,10 @@
         <v>1.91</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
         <v>1.25</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BD15" t="n">
         <v>3.42</v>
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.37</v>
+        <v>1.53</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.37</v>
+        <v>4.33</v>
       </c>
       <c r="R31" t="n">
-        <v>1.86</v>
+        <v>5.95</v>
       </c>
       <c r="S31" t="n">
-        <v>4.35</v>
+        <v>2.04</v>
       </c>
       <c r="T31" t="n">
-        <v>2.02</v>
+        <v>2.33</v>
       </c>
       <c r="U31" t="n">
-        <v>2.52</v>
+        <v>6</v>
       </c>
       <c r="V31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.43</v>
       </c>
-      <c r="W31" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z31" t="n">
-        <v>7.9</v>
+        <v>6</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ31" t="n">
         <v>1.34</v>
       </c>
-      <c r="AD31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>2.63</v>
-      </c>
       <c r="BA31" t="n">
-        <v>1.64</v>
+        <v>4.11</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE32" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q32" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R32" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U32" t="n">
-        <v>6</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W32" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ32" t="n">
+      <c r="BF32" t="n">
         <v>1.09</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.16</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>3.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.75</v>
+        <v>3.12</v>
       </c>
       <c r="R13" t="n">
-        <v>3.5</v>
+        <v>2.26</v>
       </c>
       <c r="S13" t="n">
-        <v>2.35</v>
+        <v>3.65</v>
       </c>
       <c r="T13" t="n">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="U13" t="n">
-        <v>4.14</v>
+        <v>2.7</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="W13" t="n">
-        <v>3.42</v>
+        <v>2.53</v>
       </c>
       <c r="X13" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.6</v>
+        <v>2.97</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.56</v>
+        <v>2.17</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>1.69</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.33</v>
+        <v>4.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.2</v>
+        <v>8.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="AM13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.26</v>
       </c>
-      <c r="AN13" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.13</v>
-      </c>
       <c r="BC13" t="n">
-        <v>1.76</v>
+        <v>2.29</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.85</v>
+        <v>3.34</v>
       </c>
       <c r="BE13" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.23</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.12</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>2.26</v>
+        <v>3.5</v>
       </c>
       <c r="S14" t="n">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="T14" t="n">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="U14" t="n">
-        <v>2.7</v>
+        <v>4.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>2.53</v>
+        <v>3.42</v>
       </c>
       <c r="X14" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.97</v>
+        <v>4.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.17</v>
+        <v>1.56</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="AG14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI14" t="n">
         <v>4.2</v>
       </c>
-      <c r="AH14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.34</v>
+        <v>1.89</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.55</v>
+        <v>1.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.29</v>
+        <v>1.76</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.34</v>
+        <v>4.85</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="S12" t="n">
         <v>2.55</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="U12" t="n">
-        <v>4.35</v>
+        <v>5.05</v>
       </c>
       <c r="V12" t="n">
         <v>1.48</v>
@@ -2798,7 +2798,7 @@
         <v>3.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z12" t="n">
         <v>7.6</v>
@@ -2810,22 +2810,22 @@
         <v>1.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="AE12" t="n">
         <v>2.22</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AG12" t="n">
         <v>3.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AI12" t="n">
         <v>8.5</v>
@@ -2834,10 +2834,10 @@
         <v>1.04</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AM12" t="n">
         <v>1.35</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.23</v>
+        <v>1.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.12</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.65</v>
+        <v>2.38</v>
       </c>
       <c r="T13" t="n">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7</v>
+        <v>3.52</v>
       </c>
       <c r="V13" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>2.53</v>
+        <v>3.42</v>
       </c>
       <c r="X13" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.97</v>
+        <v>4.6</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.17</v>
+        <v>1.56</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI13" t="n">
         <v>4.2</v>
       </c>
-      <c r="AH13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.55</v>
+        <v>1.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.29</v>
+        <v>1.75</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.34</v>
+        <v>4.85</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>3.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>3.5</v>
+        <v>2.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.35</v>
+        <v>3.6</v>
       </c>
       <c r="T14" t="n">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="U14" t="n">
-        <v>4.14</v>
+        <v>2.92</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="W14" t="n">
-        <v>3.42</v>
+        <v>2.53</v>
       </c>
       <c r="X14" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.6</v>
+        <v>2.96</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.56</v>
+        <v>2.17</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>1.69</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.33</v>
+        <v>4.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.2</v>
+        <v>8.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AM14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BB14" t="n">
         <v>1.26</v>
       </c>
-      <c r="AN14" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.13</v>
-      </c>
       <c r="BC14" t="n">
-        <v>1.76</v>
+        <v>2.29</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.85</v>
+        <v>3.34</v>
       </c>
       <c r="BE14" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3756,37 +3756,37 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="S17" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="U17" t="n">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W17" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="X17" t="n">
-        <v>2.99</v>
+        <v>3.29</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
         <v>1.02</v>
@@ -3798,37 +3798,37 @@
         <v>1.29</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="AF17" t="n">
         <v>1.68</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3840,31 +3840,31 @@
         <v>1.61</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AU17" t="n">
         <v>2.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AY17" t="n">
         <v>1.25</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BA17" t="n">
         <v>2.9</v>
@@ -3873,16 +3873,16 @@
         <v>1.23</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BD17" t="n">
         <v>3.58</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P30" t="n">

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S2" t="n">
         <v>2.63</v>
@@ -825,7 +825,7 @@
         <v>4.5</v>
       </c>
       <c r="X2" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="Y2" t="n">
         <v>1.83</v>
@@ -843,13 +843,13 @@
         <v>1.07</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="AE2" t="n">
         <v>1.36</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AG2" t="n">
         <v>1.83</v>
@@ -870,10 +870,10 @@
         <v>3.21</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -885,10 +885,10 @@
         <v>1.19</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AT2" t="n">
         <v>2.03</v>
@@ -903,7 +903,7 @@
         <v>2.71</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AY2" t="n">
         <v>1.65</v>
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="Q3" t="n">
         <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S3" t="n">
         <v>3.24</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V3" t="n">
         <v>1.32</v>
@@ -1043,34 +1043,34 @@
         <v>3.9</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AH3" t="n">
         <v>1.36</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>3.34</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AW3" t="n">
         <v>1.84</v>
@@ -1124,7 +1124,7 @@
         <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AL13" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.5</v>
+        <v>2.55</v>
       </c>
       <c r="BA13" t="n">
-        <v>3</v>
+        <v>1.64</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.75</v>
+        <v>2.29</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.85</v>
+        <v>3.34</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.12</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT14" t="n">
         <v>3.1</v>
       </c>
-      <c r="R14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AU14" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.55</v>
+        <v>1.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.64</v>
+        <v>3</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.29</v>
+        <v>1.75</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.34</v>
+        <v>4.85</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="S23" t="n">
         <v>2.36</v>
@@ -4974,10 +4974,10 @@
         <v>1.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AD23" t="n">
         <v>3.42</v>
@@ -4995,13 +4995,13 @@
         <v>1.28</v>
       </c>
       <c r="AI23" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="AJ23" t="n">
         <v>1.06</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AL23" t="n">
         <v>1.94</v>
@@ -5147,19 +5147,19 @@
         <v>2.05</v>
       </c>
       <c r="T24" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="U24" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="V24" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="X24" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="Y24" t="n">
         <v>1.43</v>
@@ -5174,40 +5174,40 @@
         <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.62</v>
+        <v>3.73</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AG24" t="n">
         <v>3.13</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AI24" t="n">
-        <v>6.1</v>
+        <v>6.07</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.08</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5219,10 +5219,10 @@
         <v>1.3</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AT24" t="n">
         <v>2.32</v>
@@ -5234,10 +5234,10 @@
         <v>3.07</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AY24" t="n">
         <v>1.53</v>
@@ -5249,7 +5249,7 @@
         <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
         <v>2.04</v>
@@ -5261,7 +5261,7 @@
         <v>1.73</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5335,7 +5335,7 @@
         <v>2.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="R25" t="n">
         <v>2.45</v>
@@ -5347,7 +5347,7 @@
         <v>2.04</v>
       </c>
       <c r="U25" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="V25" t="n">
         <v>1.4</v>
@@ -5359,7 +5359,7 @@
         <v>3.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z25" t="n">
         <v>8.1</v>
@@ -5371,16 +5371,16 @@
         <v>1.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AG25" t="n">
         <v>3.85</v>
@@ -5392,7 +5392,7 @@
         <v>7.8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
         <v>1.83</v>
@@ -5410,40 +5410,40 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR25" t="n">
         <v>1.85</v>
       </c>
       <c r="AS25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AW25" t="n">
         <v>2.05</v>
       </c>
-      <c r="AT25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AX25" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AZ25" t="n">
         <v>2.16</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="BB25" t="n">
         <v>1.25</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6514,19 +6514,19 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.33</v>
+        <v>4.28</v>
       </c>
       <c r="R31" t="n">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="S31" t="n">
         <v>2.04</v>
       </c>
       <c r="T31" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="U31" t="n">
         <v>6</v>
@@ -6538,13 +6538,13 @@
         <v>3.04</v>
       </c>
       <c r="X31" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z31" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AA31" t="n">
         <v>1.07</v>
@@ -6556,37 +6556,37 @@
         <v>1.23</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.44</v>
+        <v>3.95</v>
       </c>
       <c r="AE31" t="n">
         <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AG31" t="n">
         <v>3.1</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AI31" t="n">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AN31" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6598,7 +6598,7 @@
         <v>1.44</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AS31" t="n">
         <v>1.95</v>
@@ -6610,13 +6610,13 @@
         <v>3.52</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AY31" t="n">
         <v>1.38</v>
@@ -6628,19 +6628,19 @@
         <v>4.11</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6711,22 +6711,22 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>4.37</v>
+        <v>3.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="S32" t="n">
-        <v>4.35</v>
+        <v>4.8</v>
       </c>
       <c r="T32" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="U32" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="V32" t="n">
         <v>1.43</v>
@@ -6774,7 +6774,7 @@
         <v>1.06</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AL32" t="n">
         <v>1.75</v>
@@ -6783,58 +6783,58 @@
         <v>1.32</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="BB32" t="n">
         <v>1.28</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="BD32" t="n">
         <v>3.34</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="BF32" t="n">
         <v>1.09</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1825,22 +1825,22 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1855,10 +1855,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="S12" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="T12" t="n">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="U12" t="n">
-        <v>5.05</v>
+        <v>4.4</v>
       </c>
       <c r="V12" t="n">
         <v>1.48</v>
@@ -2798,10 +2798,10 @@
         <v>3.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="AA12" t="n">
         <v>1.03</v>
@@ -2810,10 +2810,10 @@
         <v>1.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AE12" t="n">
         <v>2.22</v>
@@ -2843,7 +2843,7 @@
         <v>1.35</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.12</v>
+        <v>1.85</v>
       </c>
       <c r="Q13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT13" t="n">
         <v>3.1</v>
       </c>
-      <c r="R13" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AU13" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.55</v>
+        <v>1.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.64</v>
+        <v>3</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.29</v>
+        <v>1.74</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.34</v>
+        <v>4.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.85</v>
+        <v>2.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>3.3</v>
+        <v>2.51</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>3.68</v>
       </c>
       <c r="T14" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="U14" t="n">
-        <v>3.52</v>
+        <v>3.08</v>
       </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="W14" t="n">
-        <v>3.42</v>
+        <v>2.53</v>
       </c>
       <c r="X14" t="n">
-        <v>2.25</v>
+        <v>3.04</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AW14" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM14" t="n">
+      <c r="AX14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY14" t="n">
         <v>1.21</v>
       </c>
-      <c r="AN14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AZ14" t="n">
-        <v>1.5</v>
+        <v>2.43</v>
       </c>
       <c r="BA14" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.75</v>
+        <v>2.31</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.85</v>
+        <v>3.34</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3362,37 +3362,37 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R15" t="n">
         <v>3.3</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="T15" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="U15" t="n">
-        <v>4.04</v>
+        <v>3.92</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="X15" t="n">
         <v>2.99</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AA15" t="n">
         <v>1.04</v>
@@ -3401,40 +3401,40 @@
         <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.4</v>
+        <v>3.71</v>
       </c>
       <c r="AH15" t="n">
         <v>1.23</v>
       </c>
       <c r="AI15" t="n">
-        <v>7.38</v>
+        <v>6.55</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="R16" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="S16" t="n">
         <v>2.29</v>
@@ -3577,13 +3577,13 @@
         <v>5.23</v>
       </c>
       <c r="V16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="X16" t="n">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="Y16" t="n">
         <v>1.37</v>
@@ -3601,31 +3601,31 @@
         <v>1.31</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.95</v>
+        <v>3.42</v>
       </c>
       <c r="AH16" t="n">
         <v>1.25</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.33</v>
+        <v>5.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AM16" t="n">
         <v>1.25</v>
@@ -3643,10 +3643,10 @@
         <v>1.58</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AT16" t="n">
         <v>3</v>
@@ -3655,22 +3655,22 @@
         <v>3.1</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AY16" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="BB16" t="n">
         <v>1.25</v>
@@ -3685,7 +3685,7 @@
         <v>1.63</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3756,37 +3756,37 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="S17" t="n">
         <v>2.43</v>
       </c>
       <c r="T17" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="U17" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W17" t="n">
         <v>2.69</v>
       </c>
       <c r="X17" t="n">
-        <v>3.29</v>
+        <v>3.04</v>
       </c>
       <c r="Y17" t="n">
         <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="AA17" t="n">
         <v>1.02</v>
@@ -3795,10 +3795,10 @@
         <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AE17" t="n">
         <v>2.19</v>
@@ -3813,22 +3813,22 @@
         <v>1.21</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,16 +3870,16 @@
         <v>2.9</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BC17" t="n">
         <v>2.23</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="BF17" t="n">
         <v>1.11</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BE24" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U24" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BF24" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.9</v>
+        <v>1.53</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
-        <v>2.45</v>
+        <v>6</v>
       </c>
       <c r="S25" t="n">
-        <v>3.45</v>
+        <v>2.05</v>
       </c>
       <c r="T25" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U25" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC25" t="n">
         <v>2.04</v>
       </c>
-      <c r="U25" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BD25" t="n">
-        <v>3.48</v>
+        <v>4.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.52</v>
+        <v>3.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.28</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>5.75</v>
+        <v>1.85</v>
       </c>
       <c r="S31" t="n">
-        <v>2.04</v>
+        <v>4.8</v>
       </c>
       <c r="T31" t="n">
-        <v>2.31</v>
+        <v>2.03</v>
       </c>
       <c r="U31" t="n">
-        <v>6</v>
+        <v>2.48</v>
       </c>
       <c r="V31" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W31" t="n">
-        <v>3.04</v>
+        <v>2.59</v>
       </c>
       <c r="X31" t="n">
-        <v>2.59</v>
+        <v>2.95</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.25</v>
+        <v>7.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN31" t="n">
         <v>1.23</v>
       </c>
-      <c r="AD31" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH31" t="n">
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ31" t="n">
         <v>1.32</v>
       </c>
-      <c r="AI31" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AR31" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="AV31" t="n">
         <v>2.88</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.34</v>
+        <v>2.64</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.11</v>
+        <v>1.63</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.85</v>
+        <v>3.34</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.55</v>
+        <v>1.52</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>4.28</v>
       </c>
       <c r="R32" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U32" t="n">
+        <v>6</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.85</v>
       </c>
-      <c r="S32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U32" t="n">
+      <c r="AF32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN32" t="n">
         <v>2.48</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="AU32" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="AV32" t="n">
         <v>2.88</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.64</v>
+        <v>1.34</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.63</v>
+        <v>4.11</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.34</v>
+        <v>3.85</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -2771,19 +2771,19 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="Q12" t="n">
         <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>3.75</v>
+        <v>4.52</v>
       </c>
       <c r="S12" t="n">
         <v>2.45</v>
       </c>
       <c r="T12" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="U12" t="n">
         <v>4.4</v>
@@ -2792,16 +2792,16 @@
         <v>1.48</v>
       </c>
       <c r="W12" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="X12" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Y12" t="n">
         <v>1.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA12" t="n">
         <v>1.03</v>
@@ -2810,19 +2810,19 @@
         <v>1.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AD12" t="n">
         <v>2.8</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AH12" t="n">
         <v>1.21</v>
@@ -2834,67 +2834,67 @@
         <v>1.04</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AM12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
         <v>1.35</v>
       </c>
-      <c r="AN12" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AQ12" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.55</v>
+        <v>3.92</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.65</v>
+        <v>2.79</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BA12" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="BB12" t="n">
         <v>1.27</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BD12" t="n">
         <v>3.28</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BF12" t="n">
         <v>1.12</v>
@@ -2971,10 +2971,10 @@
         <v>1.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="S13" t="n">
         <v>2.34</v>
@@ -2992,16 +2992,16 @@
         <v>3.42</v>
       </c>
       <c r="X13" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
         <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AB13" t="n">
         <v>1.02</v>
@@ -3010,16 +3010,16 @@
         <v>1.12</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
         <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AH13" t="n">
         <v>1.55</v>
@@ -3037,49 +3037,49 @@
         <v>2.47</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.1</v>
+        <v>3.72</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BA13" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BB13" t="n">
         <v>1.12</v>
@@ -3088,13 +3088,13 @@
         <v>1.74</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,22 +3165,22 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="R14" t="n">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
-        <v>3.68</v>
+        <v>3.62</v>
       </c>
       <c r="T14" t="n">
         <v>1.97</v>
       </c>
       <c r="U14" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="V14" t="n">
         <v>1.46</v>
@@ -3201,28 +3201,28 @@
         <v>1.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
         <v>1.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AG14" t="n">
-        <v>4.2</v>
+        <v>3.62</v>
       </c>
       <c r="AH14" t="n">
         <v>1.22</v>
       </c>
       <c r="AI14" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AJ14" t="n">
         <v>1.04</v>
@@ -3237,58 +3237,58 @@
         <v>1.36</v>
       </c>
       <c r="AN14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX14" t="n">
         <v>1.39</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.36</v>
       </c>
       <c r="AY14" t="n">
         <v>1.21</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="BB14" t="n">
         <v>1.26</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="BD14" t="n">
         <v>3.34</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BF14" t="n">
         <v>1.12</v>
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
         <v>3.96</v>
       </c>
       <c r="S17" t="n">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="T17" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="U17" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="V17" t="n">
         <v>1.46</v>
@@ -3798,7 +3798,7 @@
         <v>1.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
         <v>2.19</v>
@@ -3834,40 +3834,40 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AX17" t="n">
         <v>1.43</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.9</v>
+        <v>2.53</v>
       </c>
       <c r="BB17" t="n">
         <v>1.24</v>
@@ -3879,7 +3879,7 @@
         <v>3.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="BF17" t="n">
         <v>1.11</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.9</v>
+        <v>1.53</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>2.45</v>
+        <v>6</v>
       </c>
       <c r="S24" t="n">
-        <v>3.45</v>
+        <v>2.05</v>
       </c>
       <c r="T24" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U24" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC24" t="n">
         <v>2.04</v>
       </c>
-      <c r="U24" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BD24" t="n">
-        <v>3.48</v>
+        <v>4.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BE25" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U25" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BF25" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P30" t="n">

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1825,22 +1825,22 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1855,10 +1855,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2022,22 +2022,22 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2052,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BE24" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U24" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BF24" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.9</v>
+        <v>1.53</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
+        <v>6</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U25" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN25" t="n">
         <v>2.45</v>
       </c>
-      <c r="S25" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AE25" t="n">
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC25" t="n">
         <v>2.1</v>
       </c>
-      <c r="AF25" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BD25" t="n">
-        <v>3.48</v>
+        <v>4.33</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.55</v>
+        <v>1.47</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>4.28</v>
       </c>
       <c r="R31" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.85</v>
       </c>
-      <c r="S31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U31" t="n">
+      <c r="AF31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN31" t="n">
         <v>2.48</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC31" t="n">
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ31" t="n">
         <v>1.34</v>
       </c>
-      <c r="AD31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>2.64</v>
-      </c>
       <c r="BA31" t="n">
-        <v>1.63</v>
+        <v>4.11</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.52</v>
+        <v>4.38</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.28</v>
+        <v>3.38</v>
       </c>
       <c r="R32" t="n">
-        <v>5.75</v>
+        <v>1.91</v>
       </c>
       <c r="S32" t="n">
-        <v>2.04</v>
+        <v>4.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.31</v>
+        <v>2.03</v>
       </c>
       <c r="U32" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="V32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y32" t="n">
         <v>1.33</v>
       </c>
-      <c r="W32" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Z32" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.85</v>
+        <v>2.22</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="AH32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ32" t="n">
         <v>1.32</v>
       </c>
-      <c r="AI32" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AR32" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AS32" t="n">
         <v>1.95</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="AV32" t="n">
         <v>2.88</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.34</v>
+        <v>2.64</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.11</v>
+        <v>1.63</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.85</v>
+        <v>3.34</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.79</v>
+        <v>2.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="S24" t="n">
         <v>3.45</v>
@@ -5156,19 +5156,19 @@
         <v>1.45</v>
       </c>
       <c r="W24" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="X24" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z24" t="n">
         <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB24" t="n">
         <v>1.01</v>
@@ -5186,7 +5186,7 @@
         <v>1.72</v>
       </c>
       <c r="AG24" t="n">
-        <v>4.01</v>
+        <v>3.8</v>
       </c>
       <c r="AH24" t="n">
         <v>1.19</v>
@@ -5204,10 +5204,10 @@
         <v>1.89</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5225,10 +5225,10 @@
         <v>2.08</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="AV24" t="n">
         <v>2.73</v>
@@ -5240,22 +5240,22 @@
         <v>1.62</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BC24" t="n">
         <v>2.25</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="BE24" t="n">
         <v>1.53</v>
@@ -5353,10 +5353,10 @@
         <v>1.35</v>
       </c>
       <c r="W25" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X25" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Y25" t="n">
         <v>1.42</v>
@@ -5368,31 +5368,31 @@
         <v>1.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="n">
         <v>1.22</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.54</v>
+        <v>3.85</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AG25" t="n">
         <v>3.13</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AI25" t="n">
         <v>6.07</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK25" t="n">
         <v>1.85</v>
@@ -5401,10 +5401,10 @@
         <v>1.83</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5413,19 +5413,19 @@
         <v>1.16</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AS25" t="n">
         <v>1.87</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="AV25" t="n">
         <v>3.07</v>
@@ -5437,10 +5437,10 @@
         <v>1.87</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BA25" t="n">
         <v>4.2</v>
@@ -5458,7 +5458,7 @@
         <v>1.73</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.47</v>
+        <v>4.22</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.28</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>5.75</v>
+        <v>1.91</v>
       </c>
       <c r="S31" t="n">
-        <v>2.02</v>
+        <v>4.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.29</v>
+        <v>2.03</v>
       </c>
       <c r="U31" t="n">
-        <v>5.5</v>
+        <v>2.48</v>
       </c>
       <c r="V31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.33</v>
       </c>
-      <c r="W31" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Z31" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AC31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AH31" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH31" t="n">
+      <c r="AI31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ31" t="n">
         <v>1.32</v>
       </c>
-      <c r="AI31" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AR31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS31" t="n">
         <v>1.95</v>
       </c>
-      <c r="AS31" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AT31" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.99</v>
+        <v>2.13</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.34</v>
+        <v>2.64</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.11</v>
+        <v>1.63</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>4.38</v>
+        <v>1.53</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.38</v>
+        <v>4.33</v>
       </c>
       <c r="R32" t="n">
-        <v>1.91</v>
+        <v>5.75</v>
       </c>
       <c r="S32" t="n">
-        <v>4.5</v>
+        <v>2.02</v>
       </c>
       <c r="T32" t="n">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="U32" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="V32" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W32" t="n">
-        <v>2.59</v>
+        <v>3.04</v>
       </c>
       <c r="X32" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z32" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AD32" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.22</v>
+        <v>1.85</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.82</v>
+        <v>3.05</v>
       </c>
       <c r="AH32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
         <v>1.24</v>
       </c>
-      <c r="AI32" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN32" t="n">
+      <c r="AQ32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="BB32" t="n">
         <v>1.22</v>
       </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.28</v>
-      </c>
       <c r="BC32" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -804,19 +804,19 @@
         <v>2.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="R2" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="S2" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="U2" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="V2" t="n">
         <v>1.15</v>
@@ -825,7 +825,7 @@
         <v>4.5</v>
       </c>
       <c r="X2" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="Y2" t="n">
         <v>1.83</v>
@@ -840,10 +840,10 @@
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.85</v>
+        <v>6.97</v>
       </c>
       <c r="AE2" t="n">
         <v>1.36</v>
@@ -852,28 +852,28 @@
         <v>3</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH2" t="n">
         <v>1.91</v>
       </c>
       <c r="AI2" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.36</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>1.37</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AT2" t="n">
         <v>2.03</v>
@@ -921,10 +921,10 @@
         <v>1.53</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="BF2" t="n">
         <v>1.44</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1983,43 +1983,43 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
         <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC8" t="n">
         <v>1.43</v>
@@ -2031,31 +2031,31 @@
         <v>2.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
         <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>4.52</v>
+        <v>3.8</v>
       </c>
       <c r="S12" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="T12" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="U12" t="n">
-        <v>4.4</v>
+        <v>4.93</v>
       </c>
       <c r="V12" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="X12" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="AA12" t="n">
         <v>1.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.9</v>
+        <v>4.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AI12" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.04</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2861,10 +2861,10 @@
         <v>2.78</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="AV12" t="n">
         <v>2.06</v>
@@ -2876,25 +2876,25 @@
         <v>1.34</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="BF12" t="n">
         <v>1.12</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>2.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="R13" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="S13" t="n">
-        <v>2.34</v>
+        <v>3.52</v>
       </c>
       <c r="T13" t="n">
-        <v>2.36</v>
+        <v>1.97</v>
       </c>
       <c r="U13" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="W13" t="n">
-        <v>3.42</v>
+        <v>2.53</v>
       </c>
       <c r="X13" t="n">
-        <v>2.23</v>
+        <v>2.95</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.29</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.82</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.04</v>
+        <v>3.65</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3.62</v>
+        <v>2.43</v>
       </c>
       <c r="T14" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="U14" t="n">
-        <v>3.12</v>
+        <v>3.52</v>
       </c>
       <c r="V14" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>2.53</v>
+        <v>3.42</v>
       </c>
       <c r="X14" t="n">
-        <v>3.04</v>
+        <v>2.39</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AF14" t="n">
+      <c r="AQ14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AW14" t="n">
         <v>1.66</v>
       </c>
-      <c r="AG14" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AM14" t="n">
+      <c r="AX14" t="n">
         <v>1.36</v>
       </c>
-      <c r="AN14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AY14" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.9</v>
+        <v>2.88</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.29</v>
+        <v>1.79</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.34</v>
+        <v>4.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.58</v>
+        <v>2.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3362,40 +3362,40 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="S15" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="T15" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="U15" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="X15" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
         <v>8</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB15" t="n">
         <v>1.03</v>
@@ -3404,37 +3404,37 @@
         <v>1.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.71</v>
+        <v>3.79</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AI15" t="n">
-        <v>6.55</v>
+        <v>6.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AK15" t="n">
         <v>1.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AM15" t="n">
         <v>1.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3470,25 +3470,25 @@
         <v>1.33</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3559,94 +3559,94 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="R16" t="n">
         <v>4.75</v>
       </c>
       <c r="S16" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>5.23</v>
+        <v>4.6</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W16" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="X16" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AE16" t="n">
         <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.4</v>
+        <v>6.45</v>
       </c>
       <c r="AJ16" t="n">
         <v>1.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="AT16" t="n">
         <v>3</v>
@@ -3658,10 +3658,10 @@
         <v>2.3</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="AY16" t="n">
         <v>1.33</v>
@@ -3676,13 +3676,13 @@
         <v>1.25</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BD16" t="n">
         <v>3.68</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="BF16" t="n">
         <v>1.13</v>
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="S17" t="n">
         <v>2.52</v>
@@ -3771,13 +3771,13 @@
         <v>2.05</v>
       </c>
       <c r="U17" t="n">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W17" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="X17" t="n">
         <v>3.04</v>
@@ -3786,7 +3786,7 @@
         <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="AA17" t="n">
         <v>1.02</v>
@@ -3795,19 +3795,19 @@
         <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AF17" t="n">
         <v>1.68</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="AH17" t="n">
         <v>1.21</v>
@@ -3822,13 +3822,13 @@
         <v>1.87</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3861,7 +3861,7 @@
         <v>1.43</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AZ17" t="n">
         <v>1.7</v>
@@ -3870,13 +3870,13 @@
         <v>2.53</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="BE17" t="n">
         <v>1.58</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.22</v>
+        <v>1.53</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="R31" t="n">
-        <v>1.91</v>
+        <v>5.75</v>
       </c>
       <c r="S31" t="n">
-        <v>4.5</v>
+        <v>2.02</v>
       </c>
       <c r="T31" t="n">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="U31" t="n">
-        <v>2.48</v>
+        <v>5.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
-        <v>2.59</v>
+        <v>3.04</v>
       </c>
       <c r="X31" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z31" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AD31" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.22</v>
+        <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.82</v>
+        <v>3.05</v>
       </c>
       <c r="AH31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
         <v>1.24</v>
       </c>
-      <c r="AI31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN31" t="n">
+      <c r="AQ31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="BB31" t="n">
         <v>1.22</v>
       </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.28</v>
-      </c>
       <c r="BC31" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE32" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q32" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R32" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W32" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.71</v>
-      </c>
       <c r="BF32" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI32"/>
+  <dimension ref="A1:BI25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,19 +804,19 @@
         <v>2.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.85</v>
+        <v>4.14</v>
       </c>
       <c r="R2" t="n">
         <v>2.12</v>
       </c>
       <c r="S2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.8</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.84</v>
       </c>
       <c r="V2" t="n">
         <v>1.15</v>
@@ -828,7 +828,7 @@
         <v>1.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Z2" t="n">
         <v>3.88</v>
@@ -885,7 +885,7 @@
         <v>1.19</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AS2" t="n">
         <v>1.66</v>
@@ -897,13 +897,13 @@
         <v>5.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AW2" t="n">
         <v>2.71</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AY2" t="n">
         <v>1.65</v>
@@ -924,7 +924,7 @@
         <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="BF2" t="n">
         <v>1.44</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.63</v>
+        <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="R13" t="n">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="S13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U13" t="n">
         <v>3.52</v>
       </c>
-      <c r="T13" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.25</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>2.53</v>
+        <v>3.42</v>
       </c>
       <c r="X13" t="n">
-        <v>2.95</v>
+        <v>2.39</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM13" t="n">
+      <c r="AQ13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX13" t="n">
         <v>1.36</v>
       </c>
-      <c r="AN13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AY13" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.9</v>
+        <v>2.88</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.34</v>
+        <v>4.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.58</v>
+        <v>2.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="R14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U14" t="n">
         <v>3.25</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.52</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="W14" t="n">
-        <v>3.42</v>
+        <v>2.53</v>
       </c>
       <c r="X14" t="n">
-        <v>2.39</v>
+        <v>2.95</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF14" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3703,12 +3703,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,137 +3752,137 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.93</v>
+        <v>1.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="S17" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46114.6875</v>
+        <v>46114.66666666666</v>
       </c>
     </row>
     <row r="18">
@@ -3900,27 +3900,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.27</v>
+        <v>1.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="T18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR18" t="n">
         <v>1.94</v>
       </c>
-      <c r="U18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AD18" t="n">
+      <c r="AS18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BA18" t="n">
         <v>2.53</v>
       </c>
-      <c r="AE18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.27</v>
-      </c>
       <c r="BB18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.66</v>
+        <v>2.29</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46114.72916666666</v>
+        <v>46114.6875</v>
       </c>
     </row>
     <row r="19">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4294,27 +4294,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46114.72916666666</v>
+        <v>46114.75</v>
       </c>
     </row>
     <row r="21">
@@ -4491,27 +4491,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46114.72916666666</v>
+        <v>46114.79166666666</v>
       </c>
     </row>
     <row r="22">
@@ -4688,27 +4688,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46114.75</v>
+        <v>46114.79166666666</v>
       </c>
     </row>
     <row r="23">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4934,137 +4934,137 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46114.75</v>
+        <v>46114.875</v>
       </c>
     </row>
     <row r="24">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.97</v>
+        <v>1.53</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.98</v>
+        <v>4.33</v>
       </c>
       <c r="R24" t="n">
-        <v>2.17</v>
+        <v>5.75</v>
       </c>
       <c r="S24" t="n">
-        <v>3.45</v>
+        <v>2.02</v>
       </c>
       <c r="T24" t="n">
-        <v>2.04</v>
+        <v>2.29</v>
       </c>
       <c r="U24" t="n">
-        <v>2.97</v>
+        <v>5.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>2.69</v>
+        <v>3.04</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AB24" t="n">
         <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AI24" t="n">
-        <v>7.8</v>
+        <v>5.35</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.35</v>
+        <v>2.48</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.9</v>
+        <v>3.52</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AX24" t="n">
         <v>1.62</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.19</v>
+        <v>1.34</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.95</v>
+        <v>4.11</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46114.79166666666</v>
+        <v>46114.89583333334</v>
       </c>
     </row>
     <row r="25">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE25" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U25" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BF25" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5467,1385 +5467,6 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46114.79166666666</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>46114</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Waterhouse</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI26" s="3" t="n">
-        <v>46114.875</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>46114</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Greece Super League</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Asteras Tripolis</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Larissa</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI27" s="3" t="n">
-        <v>46114.875</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>46114</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Austria 2. Liga</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>SV Stripfing Weiden</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Liefering</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>canceled</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI28" s="3" t="n">
-        <v>46114.875</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46114</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Greece Super League</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Kifisia</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Panserraikos</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI29" s="3" t="n">
-        <v>46114.875</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46114</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Greece Super League</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Panaitolikos</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Atromitos</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI30" s="3" t="n">
-        <v>46114.875</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>46114</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Grêmio</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R31" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W31" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI31" s="3" t="n">
-        <v>46114.89583333334</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>46114</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Bragantino</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="S32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI32" s="3" t="n">
         <v>46114.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.04</v>
+        <v>2.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="R13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U13" t="n">
         <v>3.25</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.52</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="W13" t="n">
-        <v>3.42</v>
+        <v>2.53</v>
       </c>
       <c r="X13" t="n">
-        <v>2.39</v>
+        <v>2.95</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.63</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="R14" t="n">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="S14" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U14" t="n">
         <v>3.52</v>
       </c>
-      <c r="T14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.25</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>2.53</v>
+        <v>3.42</v>
       </c>
       <c r="X14" t="n">
-        <v>2.95</v>
+        <v>2.39</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z14" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM14" t="n">
+      <c r="AQ14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX14" t="n">
         <v>1.36</v>
       </c>
-      <c r="AN14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AY14" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.9</v>
+        <v>2.88</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.34</v>
+        <v>4.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.58</v>
+        <v>2.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,137 +3555,137 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.75</v>
+        <v>9</v>
       </c>
       <c r="S16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,137 +3752,137 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>9</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE24" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q24" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R24" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AJ24" t="n">
+      <c r="BF24" t="n">
         <v>1.09</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.22</v>
+        <v>1.53</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="R25" t="n">
-        <v>1.91</v>
+        <v>5.75</v>
       </c>
       <c r="S25" t="n">
-        <v>4.5</v>
+        <v>2.02</v>
       </c>
       <c r="T25" t="n">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="U25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN25" t="n">
         <v>2.48</v>
       </c>
-      <c r="V25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AH25" t="n">
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
         <v>1.24</v>
       </c>
-      <c r="AI25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AQ25" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.64</v>
+        <v>1.34</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.63</v>
+        <v>4.11</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.85</v>
+        <v>1.53</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="R21" t="n">
-        <v>2.45</v>
+        <v>6</v>
       </c>
       <c r="S21" t="n">
-        <v>3.45</v>
+        <v>2.05</v>
       </c>
       <c r="T21" t="n">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="U21" t="n">
-        <v>2.97</v>
+        <v>6.05</v>
       </c>
       <c r="V21" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W21" t="n">
-        <v>2.69</v>
+        <v>3.05</v>
       </c>
       <c r="X21" t="n">
-        <v>3.04</v>
+        <v>2.63</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>3.62</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.8</v>
+        <v>3.13</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AI21" t="n">
-        <v>7.8</v>
+        <v>6.07</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL21" t="n">
         <v>1.83</v>
       </c>
-      <c r="AL21" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AM21" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.42</v>
+        <v>2.48</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB21" t="n">
         <v>1.18</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.26</v>
-      </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE22" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U22" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BF22" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>4.22</v>
+        <v>1.53</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="R24" t="n">
-        <v>1.91</v>
+        <v>5.75</v>
       </c>
       <c r="S24" t="n">
-        <v>4.5</v>
+        <v>2.02</v>
       </c>
       <c r="T24" t="n">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="U24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN24" t="n">
         <v>2.48</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AH24" t="n">
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
         <v>1.24</v>
       </c>
-      <c r="AI24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AQ24" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.64</v>
+        <v>1.34</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.63</v>
+        <v>4.11</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE25" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q25" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R25" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AJ25" t="n">
+      <c r="BF25" t="n">
         <v>1.09</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="S2" t="n">
         <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="U2" t="n">
         <v>2.8</v>
@@ -831,19 +831,19 @@
         <v>1.84</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AB2" t="n">
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.97</v>
+        <v>6.95</v>
       </c>
       <c r="AE2" t="n">
         <v>1.36</v>
@@ -858,7 +858,7 @@
         <v>1.91</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.36</v>
@@ -867,7 +867,7 @@
         <v>1.28</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="AM2" t="n">
         <v>1.53</v>
@@ -879,40 +879,40 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR2" t="n">
         <v>1.41</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="BB2" t="n">
         <v>1.11</v>
@@ -998,28 +998,28 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="V3" t="n">
         <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="X3" t="n">
         <v>2.5</v>
@@ -1031,7 +1031,7 @@
         <v>5.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AB3" t="n">
         <v>1.04</v>
@@ -1040,7 +1040,7 @@
         <v>1.22</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AE3" t="n">
         <v>1.77</v>
@@ -1055,16 +1055,16 @@
         <v>1.36</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AM3" t="n">
         <v>1.65</v>
@@ -1082,22 +1082,22 @@
         <v>1.47</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AT3" t="n">
         <v>3.14</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="AV3" t="n">
         <v>2.39</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AX3" t="n">
         <v>1.48</v>
@@ -1112,7 +1112,7 @@
         <v>1.97</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC3" t="n">
         <v>1.95</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>9</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>4.75</v>
+        <v>9</v>
       </c>
       <c r="S17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R19" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -4168,10 +4168,10 @@
         <v>3.9</v>
       </c>
       <c r="V19" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="X19" t="n">
         <v>3.45</v>
@@ -4183,46 +4183,46 @@
         <v>9</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.82</v>
+        <v>4.9</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AI19" t="n">
-        <v>8.9</v>
+        <v>10.5</v>
       </c>
       <c r="AJ19" t="n">
         <v>1.01</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4237,10 +4237,10 @@
         <v>1.86</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="AU19" t="n">
         <v>3.05</v>
@@ -4255,28 +4255,28 @@
         <v>1.62</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="BA19" t="n">
         <v>2.27</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BC19" t="n">
         <v>2.66</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="BE19" t="n">
         <v>1.41</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4350,52 +4350,52 @@
         <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.61</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="S20" t="n">
         <v>2.32</v>
       </c>
       <c r="T20" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="V20" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W20" t="n">
-        <v>3.06</v>
+        <v>2.77</v>
       </c>
       <c r="X20" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="Z20" t="n">
         <v>7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AD20" t="n">
         <v>3.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AG20" t="n">
         <v>3.25</v>
@@ -4407,73 +4407,73 @@
         <v>6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AS20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AV20" t="n">
         <v>2.38</v>
       </c>
-      <c r="AT20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.23</v>
-      </c>
       <c r="AW20" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AX20" t="n">
         <v>1.47</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE21" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U21" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="AJ21" t="n">
+      <c r="BF21" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.85</v>
+        <v>1.57</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>2.45</v>
+        <v>5.5</v>
       </c>
       <c r="S22" t="n">
-        <v>3.45</v>
+        <v>2.05</v>
       </c>
       <c r="T22" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="U22" t="n">
-        <v>2.97</v>
+        <v>6</v>
       </c>
       <c r="V22" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>2.69</v>
+        <v>3.05</v>
       </c>
       <c r="X22" t="n">
-        <v>3.04</v>
+        <v>2.62</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.1</v>
+        <v>6.25</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>3.62</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AI22" t="n">
-        <v>7.8</v>
+        <v>6.06</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.42</v>
+        <v>2.5</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>1.18</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.19</v>
-      </c>
       <c r="BA22" t="n">
-        <v>1.95</v>
+        <v>5.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="S24" t="n">
         <v>2.02</v>
@@ -5156,16 +5156,16 @@
         <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>3.04</v>
+        <v>3.17</v>
       </c>
       <c r="X24" t="n">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="Y24" t="n">
         <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA24" t="n">
         <v>1.11</v>
@@ -5174,10 +5174,10 @@
         <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.44</v>
+        <v>3.77</v>
       </c>
       <c r="AE24" t="n">
         <v>1.85</v>
@@ -5186,10 +5186,10 @@
         <v>1.98</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AI24" t="n">
         <v>5.35</v>
@@ -5204,40 +5204,40 @@
         <v>1.82</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.52</v>
+        <v>3.76</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AY24" t="n">
         <v>1.47</v>
@@ -5246,16 +5246,16 @@
         <v>1.34</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.11</v>
+        <v>4.55</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
         <v>2.07</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BE24" t="n">
         <v>1.71</v>
@@ -5332,25 +5332,25 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.22</v>
+        <v>3.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S25" t="n">
         <v>4.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="U25" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W25" t="n">
         <v>2.59</v>
@@ -5362,49 +5362,49 @@
         <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="AA25" t="n">
         <v>1.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AH25" t="n">
         <v>1.24</v>
       </c>
       <c r="AI25" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AM25" t="n">
         <v>1.32</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>1.8</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="AT25" t="n">
         <v>2.56</v>
@@ -5431,7 +5431,7 @@
         <v>2.88</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="AX25" t="n">
         <v>1.58</v>
@@ -5446,7 +5446,7 @@
         <v>1.63</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
         <v>2.4</v>
@@ -5455,10 +5455,10 @@
         <v>3.34</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="R12" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U12" t="n">
-        <v>4.93</v>
+        <v>5.15</v>
       </c>
       <c r="V12" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W12" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="X12" t="n">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="AA12" t="n">
         <v>1.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AG12" t="n">
-        <v>4.31</v>
+        <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AI12" t="n">
-        <v>7</v>
+        <v>6.45</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AL12" t="n">
         <v>1.75</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BA12" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2968,16 +2968,16 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="R13" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="S13" t="n">
-        <v>3.52</v>
+        <v>3.14</v>
       </c>
       <c r="T13" t="n">
         <v>1.97</v>
@@ -2992,13 +2992,13 @@
         <v>2.53</v>
       </c>
       <c r="X13" t="n">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="Y13" t="n">
         <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="AA13" t="n">
         <v>1.03</v>
@@ -3010,19 +3010,19 @@
         <v>1.39</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AG13" t="n">
         <v>3.54</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI13" t="n">
         <v>8</v>
@@ -3031,28 +3031,28 @@
         <v>1.04</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AM13" t="n">
         <v>1.36</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="AS13" t="n">
         <v>2.63</v>
@@ -3085,13 +3085,13 @@
         <v>1.26</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BD13" t="n">
         <v>3.34</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BF13" t="n">
         <v>1.12</v>
@@ -3165,22 +3165,22 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.65</v>
+        <v>3.82</v>
       </c>
       <c r="R14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="S14" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="T14" t="n">
         <v>2.35</v>
       </c>
       <c r="U14" t="n">
-        <v>3.52</v>
+        <v>3.76</v>
       </c>
       <c r="V14" t="n">
         <v>1.25</v>
@@ -3189,10 +3189,10 @@
         <v>3.42</v>
       </c>
       <c r="X14" t="n">
-        <v>2.39</v>
+        <v>2.16</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
         <v>5</v>
@@ -3201,37 +3201,37 @@
         <v>1.13</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
         <v>1.12</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
         <v>2.35</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AJ14" t="n">
         <v>1.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AM14" t="n">
         <v>1.22</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.61</v>
@@ -3270,7 +3270,7 @@
         <v>1.36</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AZ14" t="n">
         <v>1.57</v>
@@ -3288,7 +3288,7 @@
         <v>4.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="BF14" t="n">
         <v>1.28</v>
@@ -3362,37 +3362,37 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R15" t="n">
         <v>3.2</v>
       </c>
-      <c r="R15" t="n">
-        <v>3</v>
-      </c>
       <c r="S15" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="T15" t="n">
         <v>2.15</v>
       </c>
       <c r="U15" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="V15" t="n">
         <v>1.42</v>
       </c>
       <c r="W15" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="X15" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z15" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="AA15" t="n">
         <v>1.03</v>
@@ -3401,16 +3401,16 @@
         <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AD15" t="n">
         <v>3.11</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG15" t="n">
         <v>3.79</v>
@@ -3422,13 +3422,13 @@
         <v>6.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AM15" t="n">
         <v>1.33</v>
@@ -3440,55 +3440,55 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AT15" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="BB15" t="n">
         <v>1.26</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="BD15" t="n">
         <v>3.34</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3562,52 +3562,52 @@
         <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="S16" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="U16" t="n">
-        <v>4.6</v>
+        <v>5.35</v>
       </c>
       <c r="V16" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W16" t="n">
-        <v>2.93</v>
+        <v>2.76</v>
       </c>
       <c r="X16" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC16" t="n">
         <v>1.24</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
         <v>3.37</v>
@@ -3616,76 +3616,76 @@
         <v>1.3</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.45</v>
+        <v>7.2</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="AT16" t="n">
         <v>3</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.25</v>
+        <v>4.91</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BC16" t="n">
         <v>2</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.68</v>
+        <v>3.52</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Q18" t="n">
         <v>3.2</v>
@@ -3962,52 +3962,52 @@
         <v>3.7</v>
       </c>
       <c r="S18" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T18" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="U18" t="n">
         <v>4.4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
         <v>2.7</v>
       </c>
       <c r="X18" t="n">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="AA18" t="n">
         <v>1.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="AE18" t="n">
         <v>2.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
         <v>3.62</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AI18" t="n">
         <v>7.5</v>
@@ -4016,43 +4016,43 @@
         <v>1.03</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AX18" t="n">
         <v>1.43</v>
@@ -4067,13 +4067,13 @@
         <v>2.53</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BC18" t="n">
         <v>2.29</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BE18" t="n">
         <v>1.58</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.87</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="R21" t="n">
-        <v>2.45</v>
+        <v>5.5</v>
       </c>
       <c r="S21" t="n">
-        <v>3.56</v>
+        <v>2.05</v>
       </c>
       <c r="T21" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="U21" t="n">
-        <v>2.97</v>
+        <v>6</v>
       </c>
       <c r="V21" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W21" t="n">
-        <v>2.69</v>
+        <v>3.05</v>
       </c>
       <c r="X21" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AI21" t="n">
-        <v>7.9</v>
+        <v>6.06</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS21" t="n">
         <v>1.84</v>
       </c>
-      <c r="AL21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
+      <c r="AT21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>1.18</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>2.19</v>
-      </c>
       <c r="BA21" t="n">
-        <v>1.95</v>
+        <v>5.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.57</v>
+        <v>2.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>5.5</v>
+        <v>2.45</v>
       </c>
       <c r="S22" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AW22" t="n">
         <v>2.05</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U22" t="n">
-        <v>6</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AX22" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.18</v>
+        <v>2.19</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.8</v>
+        <v>1.95</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="S24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.02</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.29</v>
-      </c>
       <c r="U24" t="n">
-        <v>5.5</v>
+        <v>2.54</v>
       </c>
       <c r="V24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.33</v>
       </c>
-      <c r="W24" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Z24" t="n">
-        <v>6.25</v>
+        <v>7.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.77</v>
+        <v>2.97</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.89</v>
+        <v>4.2</v>
       </c>
       <c r="AH24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM24" t="n">
         <v>1.32</v>
       </c>
-      <c r="AI24" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AN24" t="n">
-        <v>2.43</v>
+        <v>1.16</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.34</v>
+        <v>2.64</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.55</v>
+        <v>1.63</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.85</v>
+        <v>3.34</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.95</v>
+        <v>6</v>
       </c>
       <c r="S25" t="n">
-        <v>4.5</v>
+        <v>2.02</v>
       </c>
       <c r="T25" t="n">
-        <v>2.02</v>
+        <v>2.29</v>
       </c>
       <c r="U25" t="n">
-        <v>2.54</v>
+        <v>5.5</v>
       </c>
       <c r="V25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.44</v>
       </c>
-      <c r="W25" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z25" t="n">
-        <v>7.9</v>
+        <v>6.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.97</v>
+        <v>3.77</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.24</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AG25" t="n">
-        <v>4.2</v>
+        <v>2.89</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AI25" t="n">
-        <v>7.7</v>
+        <v>5.35</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.16</v>
+        <v>2.43</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.64</v>
+        <v>1.34</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.63</v>
+        <v>4.55</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.34</v>
+        <v>3.85</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.04</v>
+        <v>3.82</v>
       </c>
       <c r="R13" t="n">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="S13" t="n">
-        <v>3.14</v>
+        <v>2.42</v>
       </c>
       <c r="T13" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="U13" t="n">
-        <v>3.25</v>
+        <v>3.76</v>
       </c>
       <c r="V13" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>2.53</v>
+        <v>3.42</v>
       </c>
       <c r="X13" t="n">
-        <v>3.34</v>
+        <v>2.16</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AB13" t="n">
         <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.85</v>
+        <v>4.8</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.13</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AW13" t="n">
         <v>1.66</v>
       </c>
-      <c r="AG13" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM13" t="n">
+      <c r="AX13" t="n">
         <v>1.36</v>
       </c>
-      <c r="AN13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AY13" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.9</v>
+        <v>2.88</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.38</v>
+        <v>1.79</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.34</v>
+        <v>4.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.82</v>
+        <v>3.04</v>
       </c>
       <c r="R14" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="S14" t="n">
-        <v>2.42</v>
+        <v>3.14</v>
       </c>
       <c r="T14" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="U14" t="n">
-        <v>3.76</v>
+        <v>3.25</v>
       </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="W14" t="n">
-        <v>3.42</v>
+        <v>2.53</v>
       </c>
       <c r="X14" t="n">
-        <v>2.16</v>
+        <v>3.34</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AB14" t="n">
         <v>1.03</v>
       </c>
       <c r="AC14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF14" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>9</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="R19" t="n">
         <v>3.1</v>
@@ -4162,7 +4162,7 @@
         <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U19" t="n">
         <v>3.9</v>
@@ -4171,10 +4171,10 @@
         <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="X19" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Y19" t="n">
         <v>1.23</v>
@@ -4183,10 +4183,10 @@
         <v>9</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AC19" t="n">
         <v>1.5</v>
@@ -4195,25 +4195,25 @@
         <v>2.61</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AI19" t="n">
         <v>10.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL19" t="n">
         <v>1.67</v>
@@ -4234,28 +4234,28 @@
         <v>1.41</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AS19" t="n">
         <v>2.15</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.05</v>
+        <v>2.81</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.05</v>
+        <v>3.76</v>
       </c>
       <c r="AV19" t="n">
         <v>2.28</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AZ19" t="n">
         <v>1.94</v>
@@ -4276,7 +4276,7 @@
         <v>1.41</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>2.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R21" t="n">
-        <v>5.5</v>
+        <v>2.45</v>
       </c>
       <c r="S21" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AW21" t="n">
         <v>2.05</v>
       </c>
-      <c r="T21" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U21" t="n">
-        <v>6</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AX21" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.18</v>
+        <v>2.19</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.8</v>
+        <v>1.95</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.87</v>
+        <v>1.57</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>2.45</v>
+        <v>5.5</v>
       </c>
       <c r="S22" t="n">
-        <v>3.56</v>
+        <v>2.05</v>
       </c>
       <c r="T22" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="U22" t="n">
-        <v>2.97</v>
+        <v>6</v>
       </c>
       <c r="V22" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>2.69</v>
+        <v>3.05</v>
       </c>
       <c r="X22" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AI22" t="n">
-        <v>7.9</v>
+        <v>6.06</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS22" t="n">
         <v>1.84</v>
       </c>
-      <c r="AL22" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
+      <c r="AT22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>1.18</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.19</v>
-      </c>
       <c r="BA22" t="n">
-        <v>1.95</v>
+        <v>5.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.95</v>
+        <v>6</v>
       </c>
       <c r="S24" t="n">
-        <v>4.5</v>
+        <v>2.02</v>
       </c>
       <c r="T24" t="n">
-        <v>2.02</v>
+        <v>2.29</v>
       </c>
       <c r="U24" t="n">
-        <v>2.54</v>
+        <v>5.5</v>
       </c>
       <c r="V24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.44</v>
       </c>
-      <c r="W24" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z24" t="n">
-        <v>7.9</v>
+        <v>6.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.97</v>
+        <v>3.77</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.24</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AG24" t="n">
-        <v>4.2</v>
+        <v>2.89</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AI24" t="n">
-        <v>7.7</v>
+        <v>5.35</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.16</v>
+        <v>2.43</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.64</v>
+        <v>1.34</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.63</v>
+        <v>4.55</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.34</v>
+        <v>3.85</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="S25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T25" t="n">
         <v>2.02</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.29</v>
-      </c>
       <c r="U25" t="n">
-        <v>5.5</v>
+        <v>2.54</v>
       </c>
       <c r="V25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.33</v>
       </c>
-      <c r="W25" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Z25" t="n">
-        <v>6.25</v>
+        <v>7.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.77</v>
+        <v>2.97</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.89</v>
+        <v>4.2</v>
       </c>
       <c r="AH25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM25" t="n">
         <v>1.32</v>
       </c>
-      <c r="AI25" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AN25" t="n">
-        <v>2.43</v>
+        <v>1.16</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.34</v>
+        <v>2.64</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.55</v>
+        <v>1.63</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.85</v>
+        <v>3.34</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>9</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="S17" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.87</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="R21" t="n">
-        <v>2.45</v>
+        <v>5.5</v>
       </c>
       <c r="S21" t="n">
-        <v>3.56</v>
+        <v>2.05</v>
       </c>
       <c r="T21" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="U21" t="n">
-        <v>2.97</v>
+        <v>6</v>
       </c>
       <c r="V21" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W21" t="n">
-        <v>2.69</v>
+        <v>3.05</v>
       </c>
       <c r="X21" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AI21" t="n">
-        <v>7.9</v>
+        <v>6.06</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS21" t="n">
         <v>1.84</v>
       </c>
-      <c r="AL21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
+      <c r="AT21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>1.18</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>2.19</v>
-      </c>
       <c r="BA21" t="n">
-        <v>1.95</v>
+        <v>5.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.57</v>
+        <v>2.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>5.5</v>
+        <v>2.45</v>
       </c>
       <c r="S22" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AW22" t="n">
         <v>2.05</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U22" t="n">
-        <v>6</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AX22" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.18</v>
+        <v>2.19</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.8</v>
+        <v>1.95</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="S24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.02</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.29</v>
-      </c>
       <c r="U24" t="n">
-        <v>5.5</v>
+        <v>2.54</v>
       </c>
       <c r="V24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.33</v>
       </c>
-      <c r="W24" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Z24" t="n">
-        <v>6.25</v>
+        <v>7.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.77</v>
+        <v>2.97</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.89</v>
+        <v>4.2</v>
       </c>
       <c r="AH24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM24" t="n">
         <v>1.32</v>
       </c>
-      <c r="AI24" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AN24" t="n">
-        <v>2.43</v>
+        <v>1.16</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.34</v>
+        <v>2.64</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.55</v>
+        <v>1.63</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.85</v>
+        <v>3.34</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.95</v>
+        <v>6</v>
       </c>
       <c r="S25" t="n">
-        <v>4.5</v>
+        <v>2.02</v>
       </c>
       <c r="T25" t="n">
-        <v>2.02</v>
+        <v>2.29</v>
       </c>
       <c r="U25" t="n">
-        <v>2.54</v>
+        <v>5.5</v>
       </c>
       <c r="V25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.44</v>
       </c>
-      <c r="W25" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z25" t="n">
-        <v>7.9</v>
+        <v>6.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.97</v>
+        <v>3.77</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.24</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AG25" t="n">
-        <v>4.2</v>
+        <v>2.89</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AI25" t="n">
-        <v>7.7</v>
+        <v>5.35</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.16</v>
+        <v>2.43</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.64</v>
+        <v>1.34</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.63</v>
+        <v>4.55</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.34</v>
+        <v>3.85</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -801,28 +801,28 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="R2" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="S2" t="n">
         <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="U2" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="V2" t="n">
         <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="X2" t="n">
         <v>1.8</v>
@@ -831,7 +831,7 @@
         <v>1.84</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AA2" t="n">
         <v>1.21</v>
@@ -840,10 +840,10 @@
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>1.36</v>
@@ -867,10 +867,10 @@
         <v>1.28</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AN2" t="n">
         <v>1.5</v>
@@ -882,31 +882,31 @@
         <v>1.07</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AT2" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.8</v>
+        <v>5.95</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AZ2" t="n">
         <v>1.71</v>
@@ -921,7 +921,7 @@
         <v>1.53</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BE2" t="n">
         <v>2.4</v>
@@ -998,49 +998,49 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
         <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
         <v>2.7</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="X3" t="n">
         <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Z3" t="n">
         <v>5.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AB3" t="n">
         <v>1.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AE3" t="n">
         <v>1.77</v>
@@ -1049,28 +1049,28 @@
         <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.15</v>
+        <v>4.9</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1082,7 +1082,7 @@
         <v>1.47</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AS3" t="n">
         <v>2.36</v>
@@ -1112,10 +1112,10 @@
         <v>1.97</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BD3" t="n">
         <v>4</v>
@@ -1124,7 +1124,7 @@
         <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -3362,37 +3362,37 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="R15" t="n">
-        <v>3.2</v>
+        <v>3.01</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="T15" t="n">
         <v>2.15</v>
       </c>
       <c r="U15" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>2.53</v>
+        <v>2.77</v>
       </c>
       <c r="X15" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="AA15" t="n">
         <v>1.03</v>
@@ -3401,34 +3401,34 @@
         <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.79</v>
+        <v>3.54</v>
       </c>
       <c r="AH15" t="n">
         <v>1.22</v>
       </c>
       <c r="AI15" t="n">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
       <c r="AJ15" t="n">
         <v>1.04</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AM15" t="n">
         <v>1.33</v>
@@ -3452,7 +3452,7 @@
         <v>2.36</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="AU15" t="n">
         <v>3.34</v>
@@ -3464,7 +3464,7 @@
         <v>1.84</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AY15" t="n">
         <v>1.27</v>
@@ -3476,13 +3476,13 @@
         <v>2.23</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BC15" t="n">
         <v>2.27</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="BE15" t="n">
         <v>1.59</v>
@@ -3559,28 +3559,28 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="T16" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>5.35</v>
+        <v>5.51</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="X16" t="n">
         <v>2.8</v>
@@ -3598,37 +3598,37 @@
         <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD16" t="n">
         <v>3.04</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" t="n">
-        <v>7.2</v>
+        <v>5.75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AN16" t="n">
         <v>1.99</v>
@@ -3637,22 +3637,22 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.57</v>
+        <v>2.35</v>
       </c>
       <c r="AT16" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="AV16" t="n">
         <v>2.19</v>
@@ -3661,22 +3661,22 @@
         <v>1.73</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AZ16" t="n">
         <v>1.36</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.91</v>
+        <v>3.25</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="BC16" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="BD16" t="n">
         <v>3.52</v>
@@ -4150,16 +4150,16 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
         <v>2.97</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T19" t="n">
         <v>1.95</v>
@@ -4168,16 +4168,16 @@
         <v>3.9</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="X19" t="n">
         <v>3.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
         <v>9</v>
@@ -4186,37 +4186,37 @@
         <v>1.01</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AG19" t="n">
         <v>4.8</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AI19" t="n">
         <v>10.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK19" t="n">
         <v>2.05</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AM19" t="n">
         <v>1.35</v>
@@ -4237,7 +4237,7 @@
         <v>1.92</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AT19" t="n">
         <v>2.81</v>
@@ -4246,7 +4246,7 @@
         <v>3.76</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.28</v>
+        <v>2.61</v>
       </c>
       <c r="AW19" t="n">
         <v>2</v>
@@ -4255,25 +4255,25 @@
         <v>1.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AZ19" t="n">
         <v>1.94</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="BF19" t="n">
         <v>1.05</v>
@@ -4347,91 +4347,91 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="S20" t="n">
         <v>2.32</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="U20" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="V20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="X20" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB20" t="n">
         <v>1.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AI20" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="AJ20" t="n">
         <v>1.04</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AL20" t="n">
         <v>1.85</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.49</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AS20" t="n">
         <v>2.34</v>
@@ -4440,7 +4440,7 @@
         <v>3.14</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="AV20" t="n">
         <v>2.38</v>
@@ -4449,28 +4449,28 @@
         <v>1.86</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AY20" t="n">
         <v>1.27</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BA20" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BF20" t="n">
         <v>1.12</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>2.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.2</v>
+        <v>3.36</v>
       </c>
       <c r="R21" t="n">
-        <v>5.5</v>
+        <v>2.45</v>
       </c>
       <c r="S21" t="n">
-        <v>2.05</v>
+        <v>3.56</v>
       </c>
       <c r="T21" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="U21" t="n">
-        <v>6</v>
+        <v>2.88</v>
       </c>
       <c r="V21" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="W21" t="n">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="X21" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.62</v>
+        <v>2.89</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.99</v>
+        <v>1.68</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.12</v>
+        <v>3.85</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.06</v>
+        <v>8</v>
       </c>
       <c r="AJ21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BF21" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.87</v>
+        <v>1.57</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN22" t="n">
         <v>2.45</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X22" t="n">
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV22" t="n">
         <v>3.1</v>
       </c>
-      <c r="Y22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="AH22" t="n">
+      <c r="AW22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB22" t="n">
         <v>1.19</v>
       </c>
-      <c r="AI22" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AW22" t="n">
+      <c r="BC22" t="n">
         <v>2.05</v>
       </c>
-      <c r="AX22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BD22" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5141,34 +5141,34 @@
         <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="S24" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="T24" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="U24" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V24" t="n">
         <v>1.44</v>
       </c>
       <c r="W24" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="X24" t="n">
         <v>3</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB24" t="n">
         <v>1.05</v>
@@ -5177,7 +5177,7 @@
         <v>1.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="AE24" t="n">
         <v>2.24</v>
@@ -5186,10 +5186,10 @@
         <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AI24" t="n">
         <v>7.7</v>
@@ -5201,28 +5201,28 @@
         <v>1.95</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AN24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
         <v>1.16</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.26</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.32</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="AT24" t="n">
         <v>2.56</v>
@@ -5231,13 +5231,13 @@
         <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AW24" t="n">
         <v>1.94</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AY24" t="n">
         <v>1.41</v>
@@ -5252,13 +5252,13 @@
         <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="BF24" t="n">
         <v>1.12</v>
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="R25" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="S25" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="T25" t="n">
         <v>2.29</v>
       </c>
       <c r="U25" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="V25" t="n">
         <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="X25" t="n">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="Y25" t="n">
         <v>1.44</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.25</v>
+        <v>5.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.77</v>
+        <v>3.7</v>
       </c>
       <c r="AE25" t="n">
         <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="AH25" t="n">
         <v>1.32</v>
       </c>
       <c r="AI25" t="n">
-        <v>5.35</v>
+        <v>5.75</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5413,46 +5413,46 @@
         <v>1.19</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="AV25" t="n">
         <v>2.63</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.17</v>
+        <v>1.99</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AZ25" t="n">
         <v>1.34</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.55</v>
+        <v>3.7</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC25" t="n">
         <v>2.07</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="BE25" t="n">
         <v>1.71</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -801,28 +801,28 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="R2" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="S2" t="n">
         <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="U2" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W2" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="X2" t="n">
         <v>1.8</v>
@@ -843,7 +843,7 @@
         <v>1.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="AE2" t="n">
         <v>1.36</v>
@@ -870,49 +870,49 @@
         <v>3.1</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AR2" t="n">
         <v>1.49</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.95</v>
+        <v>6.15</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AY2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>1.7</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>1.71</v>
-      </c>
       <c r="BA2" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="BB2" t="n">
         <v>1.11</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -1983,34 +1983,34 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="T8" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U8" t="n">
-        <v>5.05</v>
+        <v>4.65</v>
       </c>
       <c r="V8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X8" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
         <v>8.6</v>
@@ -2019,28 +2019,28 @@
         <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AE8" t="n">
         <v>2.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
         <v>4.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AI8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.02</v>
@@ -2052,10 +2052,10 @@
         <v>1.68</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BF8" t="n">
         <v>1.09</v>
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="U12" t="n">
-        <v>5.15</v>
+        <v>4.96</v>
       </c>
       <c r="V12" t="n">
         <v>1.51</v>
@@ -2795,7 +2795,7 @@
         <v>2.39</v>
       </c>
       <c r="X12" t="n">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="n">
         <v>1.33</v>
@@ -2807,25 +2807,25 @@
         <v>1.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AE12" t="n">
         <v>2.15</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG12" t="n">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" t="n">
         <v>6.45</v>
@@ -2837,13 +2837,13 @@
         <v>1.87</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2852,13 +2852,13 @@
         <v>1.37</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AT12" t="n">
         <v>4.1</v>
@@ -2867,13 +2867,13 @@
         <v>2.71</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AY12" t="n">
         <v>1.16</v>
@@ -2885,13 +2885,13 @@
         <v>3.15</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="BE12" t="n">
         <v>1.62</v>
@@ -2968,22 +2968,22 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
         <v>2.35</v>
       </c>
       <c r="U13" t="n">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="V13" t="n">
         <v>1.25</v>
@@ -2992,55 +2992,55 @@
         <v>3.42</v>
       </c>
       <c r="X13" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
         <v>1.12</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AE13" t="n">
         <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3073,7 +3073,7 @@
         <v>1.36</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AZ13" t="n">
         <v>1.57</v>
@@ -3082,19 +3082,19 @@
         <v>2.88</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3171,16 +3171,16 @@
         <v>3.04</v>
       </c>
       <c r="R14" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="S14" t="n">
-        <v>3.14</v>
+        <v>3.52</v>
       </c>
       <c r="T14" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>3.25</v>
+        <v>3.01</v>
       </c>
       <c r="V14" t="n">
         <v>1.46</v>
@@ -3189,13 +3189,13 @@
         <v>2.53</v>
       </c>
       <c r="X14" t="n">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="Y14" t="n">
         <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="AA14" t="n">
         <v>1.03</v>
@@ -3207,13 +3207,13 @@
         <v>1.39</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.85</v>
+        <v>2.98</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG14" t="n">
         <v>3.54</v>
@@ -3222,7 +3222,7 @@
         <v>1.22</v>
       </c>
       <c r="AI14" t="n">
-        <v>8</v>
+        <v>6.85</v>
       </c>
       <c r="AJ14" t="n">
         <v>1.04</v>
@@ -3231,7 +3231,7 @@
         <v>1.83</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AM14" t="n">
         <v>1.36</v>
@@ -3243,13 +3243,13 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AS14" t="n">
         <v>2.63</v>
@@ -3282,13 +3282,13 @@
         <v>1.26</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BD14" t="n">
         <v>3.34</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="BF14" t="n">
         <v>1.12</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.75</v>
+        <v>9</v>
       </c>
       <c r="S16" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>5.51</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC17" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>9</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="Q18" t="n">
         <v>3.2</v>
@@ -3962,25 +3962,25 @@
         <v>3.7</v>
       </c>
       <c r="S18" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="T18" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="U18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="X18" t="n">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
         <v>8.1</v>
@@ -3992,79 +3992,79 @@
         <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AF18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL18" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.84</v>
       </c>
       <c r="AM18" t="n">
         <v>1.31</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.61</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="AT18" t="n">
         <v>3.35</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="AW18" t="n">
         <v>1.71</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AY18" t="n">
         <v>1.25</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="BB18" t="n">
         <v>1.24</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.87</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.36</v>
+        <v>4.2</v>
       </c>
       <c r="R21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN21" t="n">
         <v>2.45</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH21" t="n">
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>1.18</v>
       </c>
-      <c r="AI21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>2.16</v>
-      </c>
       <c r="BA21" t="n">
-        <v>1.95</v>
+        <v>5.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.57</v>
+        <v>2.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.36</v>
       </c>
       <c r="R22" t="n">
-        <v>5.5</v>
+        <v>2.45</v>
       </c>
       <c r="S22" t="n">
-        <v>2.05</v>
+        <v>3.56</v>
       </c>
       <c r="T22" t="n">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="U22" t="n">
-        <v>4.77</v>
+        <v>2.88</v>
       </c>
       <c r="V22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>1.36</v>
       </c>
-      <c r="W22" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF22" t="n">
+      <c r="AR22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BA22" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG22" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="AJ22" t="n">
+      <c r="BB22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BF22" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.16</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.9</v>
+        <v>1.53</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="S24" t="n">
         <v>2.01</v>
       </c>
-      <c r="S24" t="n">
-        <v>4.33</v>
-      </c>
       <c r="T24" t="n">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="U24" t="n">
-        <v>2.58</v>
+        <v>5.7</v>
       </c>
       <c r="V24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.44</v>
       </c>
-      <c r="W24" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y24" t="n">
+      <c r="Z24" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AI24" t="n">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.22</v>
+        <v>2.45</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.2</v>
+        <v>3.74</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.64</v>
+        <v>1.34</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.63</v>
+        <v>3.7</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.53</v>
+        <v>3.9</v>
       </c>
       <c r="Q25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S25" t="n">
         <v>4.33</v>
       </c>
-      <c r="R25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS25" t="n">
         <v>2.01</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U25" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AT25" t="n">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.34</v>
+        <v>2.64</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.7</v>
+        <v>1.63</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI25"/>
+  <dimension ref="A1:BI26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1339,27 +1339,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
-        <v>46114.41666666666</v>
+        <v>46114.3125</v>
       </c>
     </row>
     <row r="6">
@@ -1536,27 +1536,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>46114.4375</v>
+        <v>46114.41666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR13" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AS13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.29</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="S14" t="n">
         <v>2.5</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.52</v>
-      </c>
       <c r="T14" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="U14" t="n">
-        <v>3.01</v>
+        <v>3.82</v>
       </c>
       <c r="V14" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>2.53</v>
+        <v>3.42</v>
       </c>
       <c r="X14" t="n">
-        <v>3.04</v>
+        <v>2.23</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.98</v>
+        <v>4.7</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.27</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>2.34</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.54</v>
+        <v>2.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>6.85</v>
+        <v>4.2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.88</v>
+        <v>2.46</v>
       </c>
       <c r="AM14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX14" t="n">
         <v>1.36</v>
       </c>
-      <c r="AN14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR14" t="n">
+      <c r="AY14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="BE14" t="n">
         <v>2.02</v>
       </c>
-      <c r="AS14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.58</v>
-      </c>
       <c r="BF14" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,137 +4146,137 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.05</v>
+        <v>16</v>
       </c>
       <c r="T19" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="U19" t="n">
-        <v>3.9</v>
+        <v>1.42</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="W19" t="n">
-        <v>2.34</v>
+        <v>3.28</v>
       </c>
       <c r="X19" t="n">
-        <v>3.4</v>
+        <v>2.22</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="Z19" t="n">
-        <v>9</v>
+        <v>4.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.56</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.41</v>
+        <v>1.46</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.51</v>
+        <v>2.35</v>
       </c>
       <c r="AG19" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD19" t="n">
         <v>4.8</v>
       </c>
-      <c r="AH19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>2.99</v>
-      </c>
       <c r="BE19" t="n">
-        <v>1.42</v>
+        <v>2.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,134 +4347,134 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X20" t="n">
         <v>3.4</v>
       </c>
-      <c r="R20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="Y20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT20" t="n">
         <v>2.81</v>
       </c>
-      <c r="X20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="AU20" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BF20" t="n">
         <v>1.05</v>
       </c>
-      <c r="AC20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.12</v>
-      </c>
       <c r="BG20" t="n">
         <v>0</v>
       </c>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46114.75</v>
+        <v>46114.72916666666</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="S21" t="n">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="T21" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="U21" t="n">
-        <v>4.77</v>
+        <v>4.65</v>
       </c>
       <c r="V21" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>3.17</v>
+        <v>2.81</v>
       </c>
       <c r="X21" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1</v>
-      </c>
       <c r="AC21" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.62</v>
+        <v>3.14</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.13</v>
+        <v>3.42</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.08</v>
+        <v>6.9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AM21" t="n">
         <v>1.25</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.49</v>
+        <v>1.88</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.84</v>
+        <v>2.34</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.31</v>
+        <v>3.14</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.8</v>
+        <v>3.18</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46114.79166666666</v>
+        <v>46114.75</v>
       </c>
     </row>
     <row r="22">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.87</v>
+        <v>1.57</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.36</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN22" t="n">
         <v>2.45</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH22" t="n">
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>1.18</v>
       </c>
-      <c r="AI22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.16</v>
-      </c>
       <c r="BA22" t="n">
-        <v>1.95</v>
+        <v>5.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4934,137 +4934,137 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46114.875</v>
+        <v>46114.79166666666</v>
       </c>
     </row>
     <row r="24">
@@ -5082,27 +5082,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46114.89583333334</v>
+        <v>46114.875</v>
       </c>
     </row>
     <row r="25">
@@ -5467,6 +5467,203 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
+        <v>46114.89583333334</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" s="3" t="n">
         <v>46114.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="R11" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="S11" t="n">
         <v>3.12</v>
@@ -2622,7 +2622,7 @@
         <v>2.37</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG11" t="n">
         <v>4.25</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.5</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.52</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="U13" t="n">
-        <v>3.01</v>
+        <v>3.82</v>
       </c>
       <c r="V13" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>2.53</v>
+        <v>3.42</v>
       </c>
       <c r="X13" t="n">
-        <v>3.04</v>
+        <v>2.23</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.98</v>
+        <v>4.7</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.27</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.65</v>
+        <v>2.34</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.54</v>
+        <v>2.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>6.85</v>
+        <v>4.2</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.88</v>
+        <v>2.46</v>
       </c>
       <c r="AM13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX13" t="n">
         <v>1.36</v>
       </c>
-      <c r="AN13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR13" t="n">
+      <c r="AY13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="BE13" t="n">
         <v>2.02</v>
       </c>
-      <c r="AS13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.58</v>
-      </c>
       <c r="BF13" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR14" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC14" t="n">
+      <c r="AS14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF14" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.29</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>9</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>4.75</v>
+        <v>9</v>
       </c>
       <c r="S17" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>5.51</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="S12" t="n">
         <v>2.59</v>
@@ -2786,7 +2786,7 @@
         <v>2.05</v>
       </c>
       <c r="U12" t="n">
-        <v>4.96</v>
+        <v>4.91</v>
       </c>
       <c r="V12" t="n">
         <v>1.51</v>
@@ -2807,40 +2807,40 @@
         <v>1.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AH12" t="n">
         <v>1.24</v>
       </c>
       <c r="AI12" t="n">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.07</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AN12" t="n">
         <v>1.85</v>
@@ -2852,31 +2852,31 @@
         <v>1.37</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="AS12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU12" t="n">
         <v>2.7</v>
       </c>
-      <c r="AT12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.71</v>
-      </c>
       <c r="AV12" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AZ12" t="n">
         <v>1.46</v>
@@ -2885,13 +2885,13 @@
         <v>3.15</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="BE12" t="n">
         <v>1.62</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.02</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>3.46</v>
       </c>
       <c r="T13" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="U13" t="n">
-        <v>3.82</v>
+        <v>3.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="W13" t="n">
-        <v>3.42</v>
+        <v>2.53</v>
       </c>
       <c r="X13" t="n">
-        <v>2.23</v>
+        <v>3.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.29</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.04</v>
+        <v>3.86</v>
       </c>
       <c r="R14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S14" t="n">
         <v>2.5</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.52</v>
-      </c>
       <c r="T14" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>3.01</v>
+        <v>3.82</v>
       </c>
       <c r="V14" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>2.53</v>
+        <v>3.42</v>
       </c>
       <c r="X14" t="n">
-        <v>3.04</v>
+        <v>2.37</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.98</v>
+        <v>4.7</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.27</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.54</v>
+        <v>2.38</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.22</v>
+        <v>1.63</v>
       </c>
       <c r="AI14" t="n">
-        <v>6.85</v>
+        <v>4.34</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.88</v>
+        <v>2.46</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.43</v>
+        <v>1.81</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.58</v>
       </c>
       <c r="AR14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="BE14" t="n">
         <v>2.02</v>
       </c>
-      <c r="AS14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.58</v>
-      </c>
       <c r="BF14" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3362,28 +3362,28 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="R15" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="S15" t="n">
         <v>3.01</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.98</v>
       </c>
       <c r="T15" t="n">
         <v>2.15</v>
       </c>
       <c r="U15" t="n">
-        <v>3.55</v>
+        <v>3.31</v>
       </c>
       <c r="V15" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W15" t="n">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="X15" t="n">
         <v>2.95</v>
@@ -3401,25 +3401,25 @@
         <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AF15" t="n">
         <v>1.71</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.54</v>
+        <v>3.79</v>
       </c>
       <c r="AH15" t="n">
         <v>1.22</v>
       </c>
       <c r="AI15" t="n">
-        <v>6.75</v>
+        <v>7.38</v>
       </c>
       <c r="AJ15" t="n">
         <v>1.04</v>
@@ -3440,37 +3440,37 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AQ15" t="n">
         <v>1.47</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.85</v>
+        <v>3.07</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BA15" t="n">
         <v>2.23</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.75</v>
+        <v>9</v>
       </c>
       <c r="S16" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>5.51</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>9</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3956,22 +3956,22 @@
         <v>1.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>3.7</v>
+        <v>3.87</v>
       </c>
       <c r="S18" t="n">
-        <v>2.45</v>
+        <v>2.72</v>
       </c>
       <c r="T18" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="U18" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="V18" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
         <v>2.65</v>
@@ -3989,28 +3989,28 @@
         <v>1.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AD18" t="n">
         <v>2.96</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
         <v>4.13</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AI18" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AJ18" t="n">
         <v>1.07</v>
@@ -4019,52 +4019,52 @@
         <v>1.91</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AM18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.28</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.61</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.35</v>
+        <v>3.11</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="BB18" t="n">
         <v>1.24</v>
@@ -4159,70 +4159,70 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4347,16 +4347,16 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="R20" t="n">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
         <v>1.95</v>
@@ -4365,16 +4365,16 @@
         <v>3.9</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="X20" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
         <v>9</v>
@@ -4383,25 +4383,25 @@
         <v>1.01</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AG20" t="n">
         <v>4.8</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AI20" t="n">
         <v>10.5</v>
@@ -4413,43 +4413,43 @@
         <v>2.05</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AM20" t="n">
         <v>1.35</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.76</v>
+        <v>3.05</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="AW20" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AY20" t="n">
         <v>1.33</v>
@@ -4458,22 +4458,22 @@
         <v>1.94</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BC20" t="n">
         <v>2.62</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q21" t="n">
         <v>3.4</v>
@@ -4559,22 +4559,22 @@
         <v>2.11</v>
       </c>
       <c r="U21" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="V21" t="n">
         <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="X21" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Y21" t="n">
         <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
@@ -4583,19 +4583,19 @@
         <v>1.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.14</v>
+        <v>3.31</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="AH21" t="n">
         <v>1.23</v>
@@ -4616,37 +4616,37 @@
         <v>1.25</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AR21" t="n">
         <v>1.88</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AU21" t="n">
         <v>3</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AY21" t="n">
         <v>1.27</v>
@@ -4658,13 +4658,13 @@
         <v>3.18</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC21" t="n">
         <v>2.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BE21" t="n">
         <v>1.62</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.57</v>
+        <v>2.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>5.5</v>
+        <v>2.38</v>
       </c>
       <c r="S22" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS22" t="n">
         <v>2.05</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U22" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W22" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF22" t="n">
+      <c r="AT22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BA22" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG22" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="AJ22" t="n">
+      <c r="BB22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BF22" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.16</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.87</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.36</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>2.45</v>
+        <v>5.5</v>
       </c>
       <c r="S23" t="n">
-        <v>3.56</v>
+        <v>2.07</v>
       </c>
       <c r="T23" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="U23" t="n">
-        <v>2.88</v>
+        <v>4.77</v>
       </c>
       <c r="V23" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="W23" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="X23" t="n">
-        <v>3.15</v>
+        <v>2.63</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.89</v>
+        <v>3.62</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.19</v>
+        <v>1.79</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.68</v>
+        <v>1.99</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.85</v>
+        <v>3.14</v>
       </c>
       <c r="AH23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>1.18</v>
       </c>
-      <c r="AI23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
+      <c r="BA23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB23" t="n">
         <v>1.18</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC23" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5335,10 +5335,10 @@
         <v>3.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="R25" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="S25" t="n">
         <v>4.33</v>
@@ -5347,13 +5347,13 @@
         <v>2.05</v>
       </c>
       <c r="U25" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="V25" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W25" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="X25" t="n">
         <v>3</v>
@@ -5362,13 +5362,13 @@
         <v>1.32</v>
       </c>
       <c r="Z25" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
         <v>1.4</v>
@@ -5383,10 +5383,10 @@
         <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AI25" t="n">
         <v>7.7</v>
@@ -5398,13 +5398,13 @@
         <v>1.95</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AM25" t="n">
         <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5413,31 +5413,31 @@
         <v>1.16</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.01</v>
+        <v>2.23</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AZ25" t="n">
         <v>2.64</v>
@@ -5446,19 +5446,19 @@
         <v>1.63</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="BC25" t="n">
         <v>2.36</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5529,58 +5529,58 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.33</v>
+        <v>3.95</v>
       </c>
       <c r="R26" t="n">
-        <v>5.1</v>
+        <v>5.95</v>
       </c>
       <c r="S26" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
         <v>2.29</v>
       </c>
       <c r="U26" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="V26" t="n">
         <v>1.33</v>
       </c>
       <c r="W26" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="X26" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="Y26" t="n">
         <v>1.44</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
       <c r="AA26" t="n">
         <v>1.07</v>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="AE26" t="n">
         <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="AH26" t="n">
         <v>1.32</v>
@@ -5589,70 +5589,70 @@
         <v>5.75</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK26" t="n">
         <v>1.88</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.39</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AS26" t="n">
         <v>2.15</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.74</v>
+        <v>3.52</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AW26" t="n">
         <v>1.99</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BB26" t="n">
         <v>1.2</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="BD26" t="n">
         <v>3.88</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BF26" t="n">
         <v>1.17</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -801,31 +801,31 @@
         </is>
       </c>
       <c r="P2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="R2" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.4</v>
-      </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
         <v>2.63</v>
       </c>
       <c r="U2" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="X2" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Y2" t="n">
         <v>1.84</v>
@@ -870,49 +870,49 @@
         <v>3.1</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.15</v>
+        <v>5.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="BB2" t="n">
         <v>1.11</v>
@@ -924,7 +924,7 @@
         <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="BF2" t="n">
         <v>1.44</v>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.78</v>
+        <v>3.19</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S3" t="n">
         <v>3.3</v>
@@ -1013,7 +1013,7 @@
         <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="V3" t="n">
         <v>1.3</v>
@@ -1028,7 +1028,7 @@
         <v>1.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AA3" t="n">
         <v>1.07</v>
@@ -1040,7 +1040,7 @@
         <v>1.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="AE3" t="n">
         <v>1.77</v>
@@ -1055,67 +1055,67 @@
         <v>1.38</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.34</v>
+        <v>3.52</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BA3" t="n">
         <v>1.97</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BD3" t="n">
         <v>4</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.58</v>
+        <v>3.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>2.52</v>
+        <v>1.8</v>
       </c>
       <c r="S5" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="T5" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="U5" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="V5" t="n">
         <v>1.39</v>
@@ -1425,10 +1425,10 @@
         <v>7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
         <v>1.28</v>
@@ -1437,10 +1437,10 @@
         <v>3.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG5" t="n">
         <v>3.28</v>
@@ -1449,22 +1449,22 @@
         <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AM5" t="n">
         <v>1.24</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1983,49 +1983,49 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="S8" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="T8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U8" t="n">
-        <v>5</v>
+        <v>5.38</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W8" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="X8" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AE8" t="n">
         <v>2.35</v>
@@ -2034,61 +2034,61 @@
         <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.35</v>
+        <v>4.55</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AI8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AM8" t="n">
         <v>1.28</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD9" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BE9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2580,7 +2580,7 @@
         <v>2.9</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="S11" t="n">
         <v>3.12</v>
@@ -2652,34 +2652,34 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="S12" t="n">
         <v>2.59</v>
       </c>
       <c r="T12" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="U12" t="n">
-        <v>4.91</v>
+        <v>4.93</v>
       </c>
       <c r="V12" t="n">
         <v>1.51</v>
@@ -2795,7 +2795,7 @@
         <v>2.39</v>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="Y12" t="n">
         <v>1.33</v>
@@ -2810,25 +2810,25 @@
         <v>1.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AE12" t="n">
         <v>2.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="AH12" t="n">
         <v>1.24</v>
       </c>
       <c r="AI12" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.07</v>
@@ -2837,46 +2837,46 @@
         <v>1.88</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AU12" t="n">
         <v>2.7</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AZ12" t="n">
         <v>1.46</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="Q13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT13" t="n">
         <v>3.1</v>
       </c>
-      <c r="R13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ13" t="n">
+      <c r="AU13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>1.6</v>
       </c>
-      <c r="AR13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>2.15</v>
-      </c>
       <c r="BA13" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.34</v>
+        <v>4.95</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV14" t="n">
         <v>2.07</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="V14" t="n">
+      <c r="AW14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY14" t="n">
         <v>1.25</v>
       </c>
-      <c r="W14" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y14" t="n">
+      <c r="AZ14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE14" t="n">
         <v>1.58</v>
       </c>
-      <c r="Z14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC14" t="n">
+      <c r="BF14" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.29</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>9</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="S17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3956,16 +3956,16 @@
         <v>1.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="R18" t="n">
         <v>3.87</v>
       </c>
       <c r="S18" t="n">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="T18" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="U18" t="n">
         <v>4.55</v>
@@ -3989,22 +3989,22 @@
         <v>1.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
         <v>1.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AF18" t="n">
         <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="AH18" t="n">
         <v>1.23</v>
@@ -4022,43 +4022,43 @@
         <v>1.84</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.61</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.11</v>
+        <v>3.35</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AZ18" t="n">
         <v>1.57</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,137 +4146,137 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,137 +4343,137 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T20" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>3.9</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="W20" t="n">
-        <v>2.33</v>
+        <v>3.6</v>
       </c>
       <c r="X20" t="n">
-        <v>3.3</v>
+        <v>2.22</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="Z20" t="n">
-        <v>9</v>
+        <v>4.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.46</v>
+        <v>1.47</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.43</v>
+        <v>2.35</v>
       </c>
       <c r="AG20" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD20" t="n">
         <v>4.8</v>
       </c>
-      <c r="AH20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BE20" t="n">
-        <v>1.4</v>
+        <v>2.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.92</v>
+        <v>1.57</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>2.38</v>
+        <v>5.5</v>
       </c>
       <c r="S22" t="n">
-        <v>3.56</v>
+        <v>2.07</v>
       </c>
       <c r="T22" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="U22" t="n">
-        <v>2.85</v>
+        <v>4.77</v>
       </c>
       <c r="V22" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="X22" t="n">
-        <v>3.15</v>
+        <v>2.63</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="Z22" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.05</v>
+        <v>3.62</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.71</v>
+        <v>1.99</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.85</v>
+        <v>3.14</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.41</v>
+        <v>2.43</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AS22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC22" t="n">
         <v>2.05</v>
       </c>
-      <c r="AT22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BD22" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>2.92</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>5.5</v>
+        <v>2.38</v>
       </c>
       <c r="S23" t="n">
-        <v>2.07</v>
+        <v>3.56</v>
       </c>
       <c r="T23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>2.16</v>
       </c>
-      <c r="U23" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AJ23" t="n">
+      <c r="BA23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BF23" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>1.16</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.9</v>
+        <v>1.52</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.31</v>
+        <v>3.95</v>
       </c>
       <c r="R25" t="n">
-        <v>1.95</v>
+        <v>5.95</v>
       </c>
       <c r="S25" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC25" t="n">
         <v>2.05</v>
       </c>
-      <c r="U25" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BD25" t="n">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.52</v>
+        <v>3.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.95</v>
+        <v>3.31</v>
       </c>
       <c r="R26" t="n">
-        <v>5.95</v>
+        <v>1.95</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>4.33</v>
       </c>
       <c r="T26" t="n">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="U26" t="n">
-        <v>5.75</v>
+        <v>2.57</v>
       </c>
       <c r="V26" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="W26" t="n">
-        <v>3.04</v>
+        <v>2.56</v>
       </c>
       <c r="X26" t="n">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.52</v>
+        <v>2.8</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.89</v>
+        <v>3.84</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AI26" t="n">
-        <v>5.75</v>
+        <v>7.7</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.47</v>
+        <v>1.25</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.32</v>
+        <v>2.64</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.8</v>
+        <v>1.63</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.05</v>
+        <v>2.36</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.19</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>3.19</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="R4" t="n">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AE4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC4" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,113 +1786,113 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="S7" t="n">
-        <v>2.89</v>
+        <v>2.55</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U7" t="n">
-        <v>3.98</v>
+        <v>5.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="X7" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AA7" t="n">
         <v>1.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="AH7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY7" t="n">
         <v>1.12</v>
       </c>
-      <c r="AI7" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,112 +1983,112 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="S8" t="n">
-        <v>2.55</v>
+        <v>2.89</v>
       </c>
       <c r="T8" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U8" t="n">
-        <v>5.38</v>
+        <v>3.98</v>
       </c>
       <c r="V8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="X8" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.01</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.35</v>
+        <v>2.61</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AI8" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2771,37 +2771,37 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="S12" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U12" t="n">
-        <v>4.93</v>
+        <v>5.15</v>
       </c>
       <c r="V12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="X12" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="Y12" t="n">
         <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="AA12" t="n">
         <v>1.03</v>
@@ -2813,19 +2813,19 @@
         <v>1.32</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.89</v>
+        <v>3.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.38</v>
+        <v>4.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" t="n">
         <v>6.45</v>
@@ -2834,49 +2834,49 @@
         <v>1.07</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AR12" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV12" t="n">
         <v>2.07</v>
       </c>
-      <c r="AS12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.03</v>
-      </c>
       <c r="AW12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AZ12" t="n">
         <v>1.46</v>
@@ -2885,13 +2885,13 @@
         <v>3.15</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BC12" t="n">
         <v>2.22</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="BE12" t="n">
         <v>1.62</v>
@@ -2968,16 +2968,16 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.65</v>
+        <v>3.86</v>
       </c>
       <c r="R13" t="n">
         <v>3.2</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T13" t="n">
         <v>2.3</v>
@@ -2992,10 +2992,10 @@
         <v>3.42</v>
       </c>
       <c r="X13" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
         <v>4.8</v>
@@ -3022,25 +3022,25 @@
         <v>2.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.39</v>
+        <v>3.7</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK13" t="n">
         <v>1.55</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3049,10 +3049,10 @@
         <v>1.3</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AS13" t="n">
         <v>2.35</v>
@@ -3064,7 +3064,7 @@
         <v>3.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AW13" t="n">
         <v>1.79</v>
@@ -3073,7 +3073,7 @@
         <v>1.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AZ13" t="n">
         <v>1.6</v>
@@ -3168,25 +3168,25 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="T14" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>2.53</v>
+        <v>2.72</v>
       </c>
       <c r="X14" t="n">
         <v>3.04</v>
@@ -3201,43 +3201,43 @@
         <v>1.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AC14" t="n">
         <v>1.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AE14" t="n">
         <v>2.27</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG14" t="n">
         <v>3.54</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AI14" t="n">
-        <v>6.8</v>
+        <v>6.85</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3246,34 +3246,34 @@
         <v>1.31</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.36</v>
+        <v>1.94</v>
       </c>
       <c r="AS14" t="n">
         <v>2.63</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="AU14" t="n">
         <v>2.92</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="BA14" t="n">
         <v>1.9</v>
@@ -3362,28 +3362,28 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="S15" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="T15" t="n">
         <v>2.15</v>
       </c>
       <c r="U15" t="n">
-        <v>3.31</v>
+        <v>3.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="X15" t="n">
         <v>2.95</v>
@@ -3413,19 +3413,19 @@
         <v>1.71</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.79</v>
+        <v>3.54</v>
       </c>
       <c r="AH15" t="n">
         <v>1.22</v>
       </c>
       <c r="AI15" t="n">
-        <v>7.38</v>
+        <v>6.75</v>
       </c>
       <c r="AJ15" t="n">
         <v>1.04</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AL15" t="n">
         <v>1.85</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="S16" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>9</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3959,7 +3959,7 @@
         <v>3.05</v>
       </c>
       <c r="R18" t="n">
-        <v>3.87</v>
+        <v>3.66</v>
       </c>
       <c r="S18" t="n">
         <v>2.55</v>
@@ -3995,25 +3995,25 @@
         <v>1.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AF18" t="n">
         <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.17</v>
+        <v>3.6</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AI18" t="n">
         <v>8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK18" t="n">
         <v>1.91</v>
@@ -4022,10 +4022,10 @@
         <v>1.84</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4037,10 +4037,10 @@
         <v>1.61</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AT18" t="n">
         <v>3.35</v>
@@ -4055,7 +4055,7 @@
         <v>1.71</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AY18" t="n">
         <v>1.25</v>
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="R19" t="n">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -4174,7 +4174,7 @@
         <v>2.33</v>
       </c>
       <c r="X19" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="Y19" t="n">
         <v>1.22</v>
@@ -4192,7 +4192,7 @@
         <v>1.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AE19" t="n">
         <v>2.46</v>
@@ -4219,10 +4219,10 @@
         <v>1.7</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4240,10 +4240,10 @@
         <v>2.1</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.05</v>
+        <v>3.89</v>
       </c>
       <c r="AV19" t="n">
         <v>2.68</v>
@@ -4255,13 +4255,13 @@
         <v>1.65</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="BB19" t="n">
         <v>1.34</v>
@@ -4270,7 +4270,7 @@
         <v>2.62</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="BE19" t="n">
         <v>1.4</v>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.52</v>
+        <v>3.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.95</v>
+        <v>3.31</v>
       </c>
       <c r="R25" t="n">
-        <v>5.95</v>
+        <v>1.95</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>4.33</v>
       </c>
       <c r="T25" t="n">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="U25" t="n">
-        <v>5.75</v>
+        <v>2.57</v>
       </c>
       <c r="V25" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="W25" t="n">
-        <v>3.04</v>
+        <v>2.56</v>
       </c>
       <c r="X25" t="n">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.52</v>
+        <v>2.8</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.89</v>
+        <v>3.84</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AI25" t="n">
-        <v>5.75</v>
+        <v>7.7</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.47</v>
+        <v>1.25</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.32</v>
+        <v>2.64</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.8</v>
+        <v>1.63</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.05</v>
+        <v>2.36</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.9</v>
+        <v>1.52</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.31</v>
+        <v>3.95</v>
       </c>
       <c r="R26" t="n">
-        <v>1.95</v>
+        <v>5.95</v>
       </c>
       <c r="S26" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC26" t="n">
         <v>2.05</v>
       </c>
-      <c r="U26" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BD26" t="n">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>3.19</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="R3" t="n">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AE3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC3" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.19</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,112 +1786,112 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="S7" t="n">
-        <v>2.55</v>
+        <v>2.89</v>
       </c>
       <c r="T7" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>5.38</v>
+        <v>3.98</v>
       </c>
       <c r="V7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="X7" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.35</v>
+        <v>2.61</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AI7" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,113 +1983,113 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="S8" t="n">
-        <v>2.89</v>
+        <v>2.55</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U8" t="n">
-        <v>3.98</v>
+        <v>5.38</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W8" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="X8" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AA8" t="n">
         <v>1.01</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="AH8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY8" t="n">
         <v>1.12</v>
       </c>
-      <c r="AI8" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>9</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>4.53</v>
+        <v>9</v>
       </c>
       <c r="S17" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4150,31 +4150,31 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="R19" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="U19" t="n">
         <v>3.9</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W19" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="X19" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="Y19" t="n">
         <v>1.22</v>
@@ -4186,13 +4186,13 @@
         <v>1.01</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AE19" t="n">
         <v>2.46</v>
@@ -4204,7 +4204,7 @@
         <v>4.8</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AI19" t="n">
         <v>10.5</v>
@@ -4216,13 +4216,13 @@
         <v>2.05</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AR19" t="n">
         <v>1.88</v>
@@ -4261,19 +4261,19 @@
         <v>1.92</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="BB19" t="n">
         <v>1.34</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="BD19" t="n">
         <v>2.95</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BF19" t="n">
         <v>1.04</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.57</v>
+        <v>2.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>5.5</v>
+        <v>2.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.07</v>
+        <v>3.56</v>
       </c>
       <c r="T22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>2.16</v>
       </c>
-      <c r="U22" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AJ22" t="n">
+      <c r="BA22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BF22" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.16</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.92</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>2.38</v>
+        <v>5.5</v>
       </c>
       <c r="S23" t="n">
-        <v>3.56</v>
+        <v>2.07</v>
       </c>
       <c r="T23" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="U23" t="n">
-        <v>2.85</v>
+        <v>4.77</v>
       </c>
       <c r="V23" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W23" t="n">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="X23" t="n">
-        <v>3.15</v>
+        <v>2.63</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.05</v>
+        <v>3.62</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.71</v>
+        <v>1.99</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.85</v>
+        <v>3.14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.41</v>
+        <v>2.43</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AS23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC23" t="n">
         <v>2.05</v>
       </c>
-      <c r="AT23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BD23" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,113 +1786,113 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="S7" t="n">
-        <v>2.89</v>
+        <v>2.55</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U7" t="n">
-        <v>3.98</v>
+        <v>5.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="X7" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AA7" t="n">
         <v>1.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="AH7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY7" t="n">
         <v>1.12</v>
       </c>
-      <c r="AI7" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,112 +1983,112 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="S8" t="n">
-        <v>2.55</v>
+        <v>2.89</v>
       </c>
       <c r="T8" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U8" t="n">
-        <v>5.38</v>
+        <v>3.98</v>
       </c>
       <c r="V8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="X8" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.01</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.35</v>
+        <v>2.61</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AI8" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2180,22 +2180,22 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="R9" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>6.34</v>
+        <v>5.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
         <v>1.36</v>
@@ -2216,76 +2216,76 @@
         <v>1.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
         <v>1.31</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AI9" t="n">
-        <v>6.25</v>
+        <v>5.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -2297,7 +2297,7 @@
         <v>1.22</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BD9" t="n">
         <v>3.8</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.86</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U13" t="n">
         <v>3.2</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.82</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="W13" t="n">
-        <v>3.42</v>
+        <v>2.72</v>
       </c>
       <c r="X13" t="n">
-        <v>2.23</v>
+        <v>3.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AC13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.29</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>3.86</v>
       </c>
       <c r="R14" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="S14" t="n">
-        <v>3.52</v>
+        <v>2.52</v>
       </c>
       <c r="T14" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>3.2</v>
+        <v>3.82</v>
       </c>
       <c r="V14" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>2.72</v>
+        <v>3.42</v>
       </c>
       <c r="X14" t="n">
-        <v>3.04</v>
+        <v>2.23</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.85</v>
+        <v>4.7</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.27</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.54</v>
+        <v>2.38</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AI14" t="n">
-        <v>6.85</v>
+        <v>3.7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.88</v>
+        <v>2.48</v>
       </c>
       <c r="AM14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AQ14" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.34</v>
+        <v>4.95</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.53</v>
+        <v>9</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>9</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE19" t="n">
         <v>2.01</v>
       </c>
-      <c r="U19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BF19" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S20" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>2.01</v>
       </c>
       <c r="U20" t="n">
-        <v>1.42</v>
+        <v>3.9</v>
       </c>
       <c r="V20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.22</v>
       </c>
-      <c r="W20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="Z20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN20" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AL20" t="n">
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY20" t="n">
         <v>1.37</v>
       </c>
-      <c r="AM20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.7</v>
+        <v>2.63</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.8</v>
+        <v>2.95</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.01</v>
+        <v>1.44</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.92</v>
+        <v>1.57</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>2.38</v>
+        <v>5.5</v>
       </c>
       <c r="S22" t="n">
-        <v>3.56</v>
+        <v>2.07</v>
       </c>
       <c r="T22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC22" t="n">
         <v>2.04</v>
       </c>
-      <c r="U22" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BD22" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>2.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>5.5</v>
+        <v>2.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.07</v>
+        <v>3.58</v>
       </c>
       <c r="T23" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="U23" t="n">
-        <v>4.77</v>
+        <v>3.15</v>
       </c>
       <c r="V23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ23" t="n">
         <v>1.35</v>
       </c>
-      <c r="W23" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AR23" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.31</v>
+        <v>2.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.34</v>
+        <v>3.81</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.07</v>
+        <v>2.78</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.34</v>
+        <v>2.11</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.18</v>
+        <v>2.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.9</v>
+        <v>1.53</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.31</v>
+        <v>4.33</v>
       </c>
       <c r="R25" t="n">
-        <v>1.95</v>
+        <v>6</v>
       </c>
       <c r="S25" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>6</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC25" t="n">
         <v>2.05</v>
       </c>
-      <c r="U25" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BD25" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.52</v>
+        <v>3.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>5.95</v>
+        <v>1.96</v>
       </c>
       <c r="S26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.29</v>
-      </c>
       <c r="U26" t="n">
-        <v>5.75</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="W26" t="n">
-        <v>3.04</v>
+        <v>2.56</v>
       </c>
       <c r="X26" t="n">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.07</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AC26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD26" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AI26" t="n">
-        <v>5.75</v>
+        <v>7.7</v>
       </c>
       <c r="AJ26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF26" t="n">
         <v>1.09</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -1589,22 +1589,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="V6" t="n">
         <v>1.49</v>
@@ -1625,16 +1625,16 @@
         <v>1.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AF6" t="n">
         <v>1.58</v>
@@ -1646,16 +1646,16 @@
         <v>1.16</v>
       </c>
       <c r="AI6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.01</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AM6" t="n">
         <v>1.35</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,112 +1786,112 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
         <v>3.1</v>
       </c>
-      <c r="R7" t="n">
-        <v>3.95</v>
-      </c>
       <c r="S7" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>5.38</v>
+        <v>3.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="X7" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AI7" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AM7" t="n">
         <v>1.28</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,113 +1983,113 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="S8" t="n">
-        <v>2.89</v>
+        <v>2.55</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U8" t="n">
-        <v>3.98</v>
+        <v>5.38</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W8" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="X8" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AA8" t="n">
         <v>1.01</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="AH8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY8" t="n">
         <v>1.12</v>
       </c>
-      <c r="AI8" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>3.86</v>
       </c>
       <c r="R13" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="S13" t="n">
-        <v>3.52</v>
+        <v>2.52</v>
       </c>
       <c r="T13" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>3.2</v>
+        <v>3.82</v>
       </c>
       <c r="V13" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>2.72</v>
+        <v>3.42</v>
       </c>
       <c r="X13" t="n">
-        <v>3.04</v>
+        <v>2.23</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.85</v>
+        <v>4.7</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.27</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.54</v>
+        <v>2.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AI13" t="n">
-        <v>6.85</v>
+        <v>3.7</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.88</v>
+        <v>2.48</v>
       </c>
       <c r="AM13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AQ13" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.34</v>
+        <v>4.95</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.86</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U14" t="n">
         <v>3.2</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.82</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>3.42</v>
+        <v>2.72</v>
       </c>
       <c r="X14" t="n">
-        <v>2.23</v>
+        <v>3.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AC14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF14" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.29</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -4347,34 +4347,34 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="U20" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="V20" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="X20" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
         <v>9</v>
@@ -4383,25 +4383,25 @@
         <v>1.01</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.45</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.43</v>
       </c>
       <c r="AG20" t="n">
         <v>4.8</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AI20" t="n">
         <v>10.5</v>
@@ -4416,64 +4416,64 @@
         <v>1.68</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.54</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.89</v>
+        <v>3.05</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.27</v>
+        <v>3.04</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BC20" t="n">
         <v>2.63</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="BE20" t="n">
         <v>1.44</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4544,130 +4544,130 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="S21" t="n">
         <v>2.32</v>
       </c>
       <c r="T21" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
         <v>4.7</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W21" t="n">
         <v>2.77</v>
       </c>
       <c r="X21" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z21" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.31</v>
+        <v>3.14</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AL21" t="n">
         <v>1.85</v>
       </c>
       <c r="AM21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AQ21" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.29</v>
+        <v>2.42</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.05</v>
+        <v>3.29</v>
       </c>
       <c r="AU21" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.18</v>
+        <v>2.54</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="BD21" t="n">
         <v>3.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="BF21" t="n">
         <v>1.12</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE22" t="n">
         <v>1.57</v>
       </c>
-      <c r="Q22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BF22" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.93</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>2.42</v>
+        <v>5.5</v>
       </c>
       <c r="S23" t="n">
-        <v>3.58</v>
+        <v>2.13</v>
       </c>
       <c r="T23" t="n">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="U23" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="V23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.42</v>
       </c>
-      <c r="W23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z23" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AC23" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.05</v>
+        <v>3.54</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.95</v>
+        <v>2.94</v>
       </c>
       <c r="AH23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB23" t="n">
         <v>1.18</v>
       </c>
-      <c r="AI23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.24</v>
-      </c>
       <c r="BC23" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.53</v>
+        <v>3.9</v>
       </c>
       <c r="Q25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S25" t="n">
         <v>4.33</v>
       </c>
-      <c r="R25" t="n">
-        <v>6</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.3</v>
-      </c>
       <c r="U25" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="V25" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="X25" t="n">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>1.02</v>
       </c>
-      <c r="AC25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ25" t="n">
+      <c r="AK25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.09</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R26" t="n">
-        <v>1.96</v>
+        <v>5.75</v>
       </c>
       <c r="S26" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN26" t="n">
         <v>2.5</v>
       </c>
-      <c r="V26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AS26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC26" t="n">
         <v>2.05</v>
       </c>
-      <c r="AT26" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU26" t="n">
+      <c r="BD26" t="n">
         <v>4.2</v>
       </c>
-      <c r="AV26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>3.34</v>
-      </c>
       <c r="BE26" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -801,31 +801,31 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.19</v>
+        <v>4.1</v>
       </c>
       <c r="R2" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T2" t="n">
         <v>2.63</v>
       </c>
       <c r="U2" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="X2" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="Y2" t="n">
         <v>1.84</v>
@@ -843,7 +843,7 @@
         <v>1.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>1.36</v>
@@ -852,19 +852,19 @@
         <v>3</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AH2" t="n">
         <v>1.91</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.36</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AL2" t="n">
         <v>3.1</v>
@@ -879,10 +879,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AR2" t="n">
         <v>1.4</v>
@@ -891,22 +891,22 @@
         <v>1.7</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.4</v>
+        <v>4.71</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AX2" t="n">
         <v>2.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AZ2" t="n">
         <v>1.8</v>
@@ -924,7 +924,7 @@
         <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="BF2" t="n">
         <v>1.44</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.19</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>2.53</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1392,112 +1392,112 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.85</v>
+        <v>6.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>4.65</v>
+        <v>3.94</v>
       </c>
       <c r="T5" t="n">
-        <v>2.05</v>
+        <v>2.42</v>
       </c>
       <c r="U5" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="X5" t="n">
-        <v>2.79</v>
+        <v>2.31</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.28</v>
+        <v>2.49</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.7</v>
+        <v>4.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.86</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U13" t="n">
         <v>3.2</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.82</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="W13" t="n">
-        <v>3.42</v>
+        <v>2.72</v>
       </c>
       <c r="X13" t="n">
-        <v>2.23</v>
+        <v>3.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AC13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.29</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>3.86</v>
       </c>
       <c r="R14" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="S14" t="n">
-        <v>3.52</v>
+        <v>2.52</v>
       </c>
       <c r="T14" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>3.2</v>
+        <v>3.82</v>
       </c>
       <c r="V14" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>2.72</v>
+        <v>3.42</v>
       </c>
       <c r="X14" t="n">
-        <v>3.04</v>
+        <v>2.23</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.85</v>
+        <v>4.7</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.27</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.54</v>
+        <v>2.38</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AI14" t="n">
-        <v>6.85</v>
+        <v>3.7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.88</v>
+        <v>2.48</v>
       </c>
       <c r="AM14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AQ14" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.34</v>
+        <v>4.95</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="S19" t="n">
         <v>16</v>
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,134 +4347,134 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.27</v>
+        <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="R20" t="n">
-        <v>3.37</v>
+        <v>3.9</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="T20" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W20" t="n">
-        <v>2.34</v>
+        <v>2.77</v>
       </c>
       <c r="X20" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="AQ20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AX20" t="n">
         <v>1.48</v>
       </c>
-      <c r="AD20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AH20" t="n">
+      <c r="AY20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BF20" t="n">
         <v>1.12</v>
       </c>
-      <c r="AI20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.09</v>
-      </c>
       <c r="BG20" t="n">
         <v>0</v>
       </c>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46114.72916666666</v>
+        <v>46114.75</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R21" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="S21" t="n">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="U21" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="X21" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AB21" t="n">
         <v>1.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.14</v>
+        <v>3.54</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.48</v>
+        <v>2.94</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AI21" t="n">
-        <v>7.1</v>
+        <v>6.29</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>1.25</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.69</v>
-      </c>
       <c r="BA21" t="n">
-        <v>2.54</v>
+        <v>4</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46114.75</v>
+        <v>46114.79166666666</v>
       </c>
     </row>
     <row r="22">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>2.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>2.97</v>
       </c>
       <c r="R23" t="n">
-        <v>5.5</v>
+        <v>3.37</v>
       </c>
       <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AS23" t="n">
         <v>2.13</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AH23" t="n">
+      <c r="AT23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB23" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI23" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC23" t="n">
-        <v>2.04</v>
+        <v>2.59</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.05</v>
+        <v>2.99</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.9</v>
+        <v>1.53</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R25" t="n">
-        <v>1.95</v>
+        <v>5.75</v>
       </c>
       <c r="S25" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN25" t="n">
         <v>2.5</v>
       </c>
-      <c r="V25" t="n">
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY25" t="n">
         <v>1.4</v>
       </c>
-      <c r="W25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM25" t="n">
+      <c r="AZ25" t="n">
         <v>1.33</v>
       </c>
-      <c r="AN25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.27</v>
-      </c>
       <c r="BA25" t="n">
-        <v>1.83</v>
+        <v>3.7</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.36</v>
+        <v>2.05</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.53</v>
+        <v>3.9</v>
       </c>
       <c r="Q26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S26" t="n">
         <v>4.33</v>
       </c>
-      <c r="R26" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.3</v>
-      </c>
       <c r="U26" t="n">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM26" t="n">
         <v>1.33</v>
       </c>
-      <c r="W26" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ26" t="n">
+      <c r="AN26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF26" t="n">
         <v>1.09</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,112 +1786,112 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U7" t="n">
-        <v>3.96</v>
+        <v>5.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="X7" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AA7" t="n">
         <v>1.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AI7" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AM7" t="n">
         <v>1.28</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,112 +1983,112 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>3.1</v>
       </c>
-      <c r="R8" t="n">
-        <v>3.95</v>
-      </c>
       <c r="S8" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U8" t="n">
-        <v>5.38</v>
+        <v>3.96</v>
       </c>
       <c r="V8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="X8" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.01</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AI8" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AM8" t="n">
         <v>1.28</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="S9" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U9" t="n">
         <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>2.73</v>
+        <v>2.97</v>
       </c>
       <c r="X9" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB9" t="n">
         <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.09</v>
+        <v>3.58</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.4</v>
+        <v>5.55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK9" t="n">
         <v>1.84</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AM9" t="n">
-        <v>2.3</v>
+        <v>1.16</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2264,7 +2264,7 @@
         <v>1.67</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="AS9" t="n">
         <v>2.77</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BC9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>3.86</v>
       </c>
       <c r="R13" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="S13" t="n">
-        <v>3.52</v>
+        <v>2.52</v>
       </c>
       <c r="T13" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>3.2</v>
+        <v>3.82</v>
       </c>
       <c r="V13" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>2.72</v>
+        <v>3.42</v>
       </c>
       <c r="X13" t="n">
-        <v>3.04</v>
+        <v>2.23</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.85</v>
+        <v>4.7</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.27</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.54</v>
+        <v>2.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AI13" t="n">
-        <v>6.85</v>
+        <v>3.7</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.88</v>
+        <v>2.48</v>
       </c>
       <c r="AM13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AQ13" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.34</v>
+        <v>4.95</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.86</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U14" t="n">
         <v>3.2</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.82</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>3.42</v>
+        <v>2.72</v>
       </c>
       <c r="X14" t="n">
-        <v>2.23</v>
+        <v>3.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AC14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF14" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.29</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="R16" t="n">
-        <v>9</v>
+        <v>11.02</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE21" t="n">
         <v>1.57</v>
       </c>
-      <c r="Q21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BF21" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.87</v>
+        <v>2.27</v>
       </c>
       <c r="Q22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="X22" t="n">
         <v>3.3</v>
       </c>
-      <c r="R22" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.95</v>
-      </c>
       <c r="Y22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY22" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ22" t="n">
+      <c r="AZ22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF22" t="n">
         <v>1.06</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.09</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.27</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.97</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>3.37</v>
+        <v>5.5</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="T23" t="n">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="U23" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT23" t="n">
         <v>2.31</v>
       </c>
-      <c r="X23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ23" t="n">
+      <c r="AU23" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AY23" t="n">
         <v>1.54</v>
       </c>
-      <c r="AR23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AZ23" t="n">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.04</v>
+        <v>4</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.59</v>
+        <v>2.04</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.99</v>
+        <v>4.05</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.53</v>
+        <v>3.9</v>
       </c>
       <c r="Q25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S25" t="n">
         <v>4.33</v>
       </c>
-      <c r="R25" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.3</v>
-      </c>
       <c r="U25" t="n">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="V25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM25" t="n">
         <v>1.33</v>
       </c>
-      <c r="W25" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ25" t="n">
+      <c r="AN25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.09</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.9</v>
+        <v>1.53</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R26" t="n">
-        <v>1.95</v>
+        <v>5.75</v>
       </c>
       <c r="S26" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN26" t="n">
         <v>2.5</v>
       </c>
-      <c r="V26" t="n">
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY26" t="n">
         <v>1.4</v>
       </c>
-      <c r="W26" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM26" t="n">
+      <c r="AZ26" t="n">
         <v>1.33</v>
       </c>
-      <c r="AN26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>2.27</v>
-      </c>
       <c r="BA26" t="n">
-        <v>1.83</v>
+        <v>3.7</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.36</v>
+        <v>2.05</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -772,42 +772,42 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q2" t="n">
         <v>4.1</v>
       </c>
       <c r="R2" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S2" t="n">
         <v>2.75</v>
@@ -825,16 +825,16 @@
         <v>4.4</v>
       </c>
       <c r="X2" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AB2" t="n">
         <v>1.01</v>
@@ -843,7 +843,7 @@
         <v>1.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="AE2" t="n">
         <v>1.36</v>
@@ -852,79 +852,79 @@
         <v>3</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.36</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AM2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AR2" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AS2" t="n">
         <v>1.7</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.71</v>
+        <v>5.19</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BB2" t="n">
         <v>1.11</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="BD2" t="n">
         <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BF2" t="n">
         <v>1.44</v>
@@ -969,42 +969,42 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1184,33 +1184,33 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q4" t="n">
         <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S4" t="n">
         <v>3.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="V4" t="n">
         <v>1.3</v>
@@ -1219,19 +1219,19 @@
         <v>3.18</v>
       </c>
       <c r="X4" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="Z4" t="n">
         <v>5.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC4" t="n">
         <v>1.22</v>
@@ -1240,31 +1240,31 @@
         <v>3.75</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="AN4" t="n">
         <v>1.33</v>
@@ -1279,10 +1279,10 @@
         <v>1.57</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AT4" t="n">
         <v>2.83</v>
@@ -1294,7 +1294,7 @@
         <v>2.37</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AX4" t="n">
         <v>1.65</v>
@@ -1303,25 +1303,25 @@
         <v>1.38</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BC4" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1375,20 +1375,20 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="R10" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.86</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U13" t="n">
         <v>3.2</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.82</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="W13" t="n">
-        <v>3.42</v>
+        <v>2.72</v>
       </c>
       <c r="X13" t="n">
-        <v>2.23</v>
+        <v>3.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AC13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.29</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>3.86</v>
       </c>
       <c r="R14" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="S14" t="n">
-        <v>3.52</v>
+        <v>2.52</v>
       </c>
       <c r="T14" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>3.2</v>
+        <v>3.82</v>
       </c>
       <c r="V14" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>2.72</v>
+        <v>3.42</v>
       </c>
       <c r="X14" t="n">
-        <v>3.04</v>
+        <v>2.23</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.85</v>
+        <v>4.7</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.27</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.54</v>
+        <v>2.38</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AI14" t="n">
-        <v>6.85</v>
+        <v>3.7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.88</v>
+        <v>2.48</v>
       </c>
       <c r="AM14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AQ14" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.34</v>
+        <v>4.95</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.18</v>
+        <v>1.73</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>11.02</v>
+        <v>4.53</v>
       </c>
       <c r="S16" t="n">
-        <v>1.67</v>
+        <v>2.34</v>
       </c>
       <c r="T16" t="n">
-        <v>2.57</v>
+        <v>2.14</v>
       </c>
       <c r="U16" t="n">
-        <v>9.640000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="V16" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="W16" t="n">
-        <v>2.97</v>
+        <v>2.66</v>
       </c>
       <c r="X16" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.21</v>
       </c>
-      <c r="AD16" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AI16" t="n">
-        <v>5.3</v>
+        <v>7.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.78</v>
+        <v>1.93</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.38</v>
+        <v>1.97</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.86</v>
+        <v>2.03</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.94</v>
+        <v>2.27</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.73</v>
+        <v>1.18</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="R17" t="n">
-        <v>4.53</v>
+        <v>11.02</v>
       </c>
       <c r="S17" t="n">
-        <v>2.34</v>
+        <v>1.67</v>
       </c>
       <c r="T17" t="n">
-        <v>2.14</v>
+        <v>2.57</v>
       </c>
       <c r="U17" t="n">
-        <v>4.8</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="W17" t="n">
-        <v>2.66</v>
+        <v>2.97</v>
       </c>
       <c r="X17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG17" t="n">
         <v>2.88</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AH17" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH17" t="n">
+      <c r="AI17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BF17" t="n">
         <v>1.21</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.11</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.87</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="R21" t="n">
-        <v>2.42</v>
+        <v>5.5</v>
       </c>
       <c r="S21" t="n">
-        <v>3.45</v>
+        <v>2.13</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="X21" t="n">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="Z21" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AC21" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.11</v>
+        <v>3.54</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.85</v>
+        <v>2.94</v>
       </c>
       <c r="AH21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB21" t="n">
         <v>1.18</v>
       </c>
-      <c r="AI21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE23" t="n">
         <v>1.57</v>
       </c>
-      <c r="Q23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BF23" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.9</v>
+        <v>1.53</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R25" t="n">
-        <v>1.95</v>
+        <v>5.75</v>
       </c>
       <c r="S25" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN25" t="n">
         <v>2.5</v>
       </c>
-      <c r="V25" t="n">
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY25" t="n">
         <v>1.4</v>
       </c>
-      <c r="W25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM25" t="n">
+      <c r="AZ25" t="n">
         <v>1.33</v>
       </c>
-      <c r="AN25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.27</v>
-      </c>
       <c r="BA25" t="n">
-        <v>1.83</v>
+        <v>3.7</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.36</v>
+        <v>2.05</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.53</v>
+        <v>3.9</v>
       </c>
       <c r="Q26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S26" t="n">
         <v>4.33</v>
       </c>
-      <c r="R26" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.3</v>
-      </c>
       <c r="U26" t="n">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM26" t="n">
         <v>1.33</v>
       </c>
-      <c r="W26" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ26" t="n">
+      <c r="AN26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF26" t="n">
         <v>1.09</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,37 +960,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,37 +1157,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3.25</v>
       </c>
-      <c r="Q4" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R4" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1560,13 +1560,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1575,27 +1575,27 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R6" t="n">
         <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.9</v>
       </c>
       <c r="S6" t="n">
         <v>2.8</v>
@@ -1604,13 +1604,13 @@
         <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="V6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="X6" t="n">
         <v>3.28</v>
@@ -1622,40 +1622,40 @@
         <v>8.6</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.03</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
         <v>1.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AF6" t="n">
         <v>1.58</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AH6" t="n">
         <v>1.16</v>
       </c>
       <c r="AI6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.01</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AM6" t="n">
         <v>1.35</v>
@@ -1667,40 +1667,40 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BB6" t="n">
         <v>1.27</v>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1769,96 +1769,96 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T7" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.88</v>
-      </c>
       <c r="U7" t="n">
-        <v>5.38</v>
+        <v>5.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W7" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="X7" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB7" t="n">
         <v>1.06</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.35</v>
+        <v>2.58</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AI7" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.11</v>
+        <v>2.79</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1954,13 +1954,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1972,33 +1972,33 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="T8" t="n">
         <v>1.9</v>
       </c>
       <c r="U8" t="n">
-        <v>3.96</v>
+        <v>3.73</v>
       </c>
       <c r="V8" t="n">
         <v>1.5</v>
@@ -2013,7 +2013,7 @@
         <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AA8" t="n">
         <v>1.01</v>
@@ -2022,16 +2022,16 @@
         <v>1.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AE8" t="n">
         <v>2.42</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG8" t="n">
         <v>4.7</v>
@@ -2046,55 +2046,55 @@
         <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AM8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
         <v>1.28</v>
       </c>
-      <c r="AN8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BB8" t="n">
         <v>1.33</v>
@@ -2109,7 +2109,7 @@
         <v>1.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2151,32 +2151,32 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2288,10 +2288,10 @@
         <v>1.17</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB9" t="n">
         <v>1.21</v>
@@ -2574,64 +2574,64 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="R11" t="n">
-        <v>2.94</v>
+        <v>3.78</v>
       </c>
       <c r="S11" t="n">
-        <v>3.12</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="U11" t="n">
-        <v>4.01</v>
+        <v>4.17</v>
       </c>
       <c r="V11" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="X11" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AI11" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ11" t="n">
         <v>1.02</v>
@@ -2640,13 +2640,13 @@
         <v>1.91</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>1.54</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AS11" t="n">
         <v>2.46</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BC11" t="n">
         <v>2.39</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="BE11" t="n">
         <v>1.47</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>7.71</v>
       </c>
       <c r="R19" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="S19" t="n">
         <v>16</v>
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="S20" t="n">
         <v>2.32</v>
@@ -4362,64 +4362,64 @@
         <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="V20" t="n">
         <v>1.38</v>
       </c>
       <c r="W20" t="n">
-        <v>2.77</v>
+        <v>2.97</v>
       </c>
       <c r="X20" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AE20" t="n">
         <v>2.07</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AI20" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL20" t="n">
         <v>1.85</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4440,7 +4440,7 @@
         <v>3.29</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="AV20" t="n">
         <v>2.3</v>
@@ -4458,22 +4458,22 @@
         <v>1.69</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BB20" t="n">
         <v>1.25</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
         <v>5.5</v>
       </c>
       <c r="S21" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="T21" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
         <v>5.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W21" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="X21" t="n">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="AF21" t="n">
         <v>1.95</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.94</v>
+        <v>3.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.29</v>
+        <v>7.35</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AL21" t="n">
         <v>1.84</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4628,7 +4628,7 @@
         <v>1.34</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AS21" t="n">
         <v>1.86</v>
@@ -4640,13 +4640,13 @@
         <v>4.37</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AW21" t="n">
         <v>2.35</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AY21" t="n">
         <v>1.54</v>
@@ -4658,19 +4658,19 @@
         <v>4</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>2.27</v>
       </c>
-      <c r="Q22" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="R22" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.61</v>
-      </c>
       <c r="BA22" t="n">
-        <v>3.04</v>
+        <v>1.95</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,130 +4938,130 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.87</v>
+        <v>2.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="R23" t="n">
-        <v>2.42</v>
+        <v>3.37</v>
       </c>
       <c r="S23" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK23" t="n">
         <v>2</v>
       </c>
-      <c r="U23" t="n">
-        <v>3</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AL23" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="AT23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV23" t="n">
         <v>2.6</v>
       </c>
-      <c r="AU23" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.78</v>
-      </c>
       <c r="AW23" t="n">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.4</v>
+        <v>1.61</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.95</v>
+        <v>3.04</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="BF23" t="n">
         <v>1.09</v>
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="R25" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="U25" t="n">
-        <v>5.4</v>
+        <v>5.22</v>
       </c>
       <c r="V25" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W25" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="X25" t="n">
-        <v>2.79</v>
+        <v>2.59</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.9</v>
+        <v>6.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB25" t="n">
         <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.87</v>
+        <v>3.8</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AI25" t="n">
-        <v>5.3</v>
+        <v>4.75</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AK25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL25" t="n">
         <v>1.88</v>
       </c>
-      <c r="AL25" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AM25" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5413,52 +5413,52 @@
         <v>1.23</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.59</v>
+        <v>3.75</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="BB25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.2</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5529,25 +5529,25 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S26" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U26" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="V26" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W26" t="n">
         <v>2.56</v>
@@ -5559,7 +5559,7 @@
         <v>1.32</v>
       </c>
       <c r="Z26" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AA26" t="n">
         <v>1.02</v>
@@ -5577,28 +5577,28 @@
         <v>2.25</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.85</v>
+        <v>4.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AI26" t="n">
-        <v>7.7</v>
+        <v>9.5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AN26" t="n">
         <v>1.25</v>
@@ -5607,52 +5607,52 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.81</v>
+        <v>3.68</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AY26" t="n">
         <v>1.45</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="BB26" t="n">
         <v>1.28</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BD26" t="n">
         <v>3.34</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BF26" t="n">
         <v>1.09</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,37 +960,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3.25</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R3" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,37 +1157,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1738,181 +1738,181 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="N7" t="n">
+        <v>7</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>7</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R7" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AK7" t="n">
-        <v>2.79</v>
+        <v>2.04</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AN7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.74</v>
+        <v>1.87</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.06</v>
+        <v>2.33</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.43</v>
+        <v>3.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.54</v>
+        <v>3.7</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,181 +1935,181 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AN8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>7</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AS8" t="n">
         <v>3.06</v>
       </c>
-      <c r="T8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD8" t="n">
+      <c r="AT8" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AU8" t="n">
         <v>2.54</v>
       </c>
-      <c r="AE8" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AH8" t="n">
+      <c r="AV8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY8" t="n">
         <v>1.12</v>
       </c>
-      <c r="AI8" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2348,42 +2348,42 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R10" t="n">
-        <v>5</v>
+        <v>5.37</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2545,32 +2545,32 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -2754,150 +2754,150 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="R12" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="S12" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>5.15</v>
+        <v>5.9</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W12" t="n">
-        <v>2.41</v>
+        <v>2.79</v>
       </c>
       <c r="X12" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="AA12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AC12" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.08</v>
+        <v>3.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AG12" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI12" t="n">
-        <v>6.45</v>
+        <v>5.9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.47</v>
+        <v>2.11</v>
       </c>
       <c r="AS12" t="n">
         <v>2.75</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AW12" t="n">
         <v>1.65</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,171 +2930,171 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R13" t="n">
         <v>3</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU13" t="n">
         <v>3</v>
       </c>
-      <c r="R13" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.92</v>
-      </c>
       <c r="AV13" t="n">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.9</v>
+        <v>2.99</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.34</v>
+        <v>5.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.58</v>
+        <v>2.11</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -3154,144 +3154,144 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BA14" t="n">
         <v>1.96</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX14" t="n">
+      <c r="BB14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="BE14" t="n">
         <v>1.5</v>
       </c>
-      <c r="AY14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BF14" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="R15" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="S15" t="n">
-        <v>2.99</v>
+        <v>2.78</v>
       </c>
       <c r="T15" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="U15" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="X15" t="n">
         <v>2.95</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AA15" t="n">
         <v>1.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AC15" t="n">
         <v>1.32</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="AH15" t="n">
         <v>1.22</v>
       </c>
       <c r="AI15" t="n">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3443,13 +3443,13 @@
         <v>1.28</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="AT15" t="n">
         <v>3.07</v>
@@ -3458,7 +3458,7 @@
         <v>3.18</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="AW15" t="n">
         <v>1.87</v>
@@ -3470,22 +3470,22 @@
         <v>1.32</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.23</v>
+        <v>2.52</v>
       </c>
       <c r="BB15" t="n">
         <v>1.25</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="BD15" t="n">
         <v>3.42</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BF15" t="n">
         <v>1.13</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.73</v>
+        <v>1.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="R16" t="n">
-        <v>4.53</v>
+        <v>13</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>1.64</v>
       </c>
       <c r="T16" t="n">
-        <v>2.14</v>
+        <v>2.66</v>
       </c>
       <c r="U16" t="n">
-        <v>4.8</v>
+        <v>8.49</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="W16" t="n">
-        <v>2.66</v>
+        <v>3.09</v>
       </c>
       <c r="X16" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AB16" t="n">
         <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.04</v>
+        <v>4.45</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.72</v>
+        <v>2.27</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="AI16" t="n">
-        <v>7.3</v>
+        <v>4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.97</v>
+        <v>1.52</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.03</v>
+        <v>3.95</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AR16" t="n">
         <v>1.88</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.54</v>
+        <v>2.1</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.02</v>
+        <v>3.88</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.21</v>
+        <v>2.68</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.37</v>
+        <v>1.11</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.75</v>
+        <v>9.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.27</v>
+        <v>1.74</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.44</v>
+        <v>5.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R17" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.18</v>
       </c>
-      <c r="Q17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>11.02</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="U17" t="n">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AN17" t="n">
-        <v>3.86</v>
+        <v>2.06</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3953,64 +3953,64 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="R18" t="n">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="S18" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U18" t="n">
-        <v>4.55</v>
+        <v>4.72</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="X18" t="n">
-        <v>3.04</v>
+        <v>3.46</v>
       </c>
       <c r="Y18" t="n">
         <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>1.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AD18" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AI18" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="AJ18" t="n">
         <v>1.03</v>
@@ -4019,64 +4019,64 @@
         <v>1.91</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AV18" t="n">
         <v>2.22</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AY18" t="n">
         <v>1.25</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BA18" t="n">
         <v>3</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="BF18" t="n">
         <v>1.11</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,130 +4741,130 @@
         </is>
       </c>
       <c r="P22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="S22" t="n">
         <v>3</v>
       </c>
-      <c r="Q22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.55</v>
-      </c>
       <c r="T22" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="U22" t="n">
-        <v>2.92</v>
+        <v>4.23</v>
       </c>
       <c r="V22" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="X22" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="Z22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AK22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB22" t="n">
         <v>1.33</v>
       </c>
-      <c r="AD22" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.27</v>
-      </c>
       <c r="BC22" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="BF22" t="n">
         <v>1.09</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,130 +4938,130 @@
         </is>
       </c>
       <c r="P23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>2.27</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="R23" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U23" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="BA23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB23" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BC23" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="BF23" t="n">
         <v>1.09</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.52</v>
+        <v>3.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="S25" t="n">
-        <v>1.97</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.33</v>
+        <v>1.99</v>
       </c>
       <c r="U25" t="n">
-        <v>5.22</v>
+        <v>2.65</v>
       </c>
       <c r="V25" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="W25" t="n">
-        <v>3.15</v>
+        <v>2.56</v>
       </c>
       <c r="X25" t="n">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.25</v>
+        <v>7.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.21</v>
+        <v>1.69</v>
       </c>
       <c r="AG25" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>4.75</v>
+        <v>9.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AM25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AQ25" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AS25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW25" t="n">
         <v>2.15</v>
       </c>
-      <c r="AT25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.03</v>
-      </c>
       <c r="AX25" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.3</v>
+        <v>2.16</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.25</v>
+        <v>3.34</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.6</v>
+        <v>1.52</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="R26" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>1.97</v>
       </c>
       <c r="T26" t="n">
-        <v>1.99</v>
+        <v>2.33</v>
       </c>
       <c r="U26" t="n">
-        <v>2.65</v>
+        <v>5.22</v>
       </c>
       <c r="V26" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="W26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN26" t="n">
         <v>2.56</v>
       </c>
-      <c r="X26" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG26" t="n">
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD26" t="n">
         <v>4.25</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="BE26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF26" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.09</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -2930,171 +2930,171 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>8</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U13" t="n">
+      <c r="AS13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD13" t="n">
         <v>3.64</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ13" t="n">
+      <c r="BE13" t="n">
         <v>1.5</v>
       </c>
-      <c r="BA13" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.11</v>
-      </c>
       <c r="BF13" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,171 +3127,171 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>1</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R14" t="n">
         <v>3</v>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU14" t="n">
         <v>3</v>
       </c>
-      <c r="R14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE14" t="n">
+      <c r="AV14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE14" t="n">
         <v>2.11</v>
       </c>
-      <c r="AF14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AN14" t="n">
+      <c r="BF14" t="n">
         <v>1.32</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3351,14 +3351,14 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3530,32 +3530,32 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3727,13 +3727,13 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -3742,17 +3742,17 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3924,16 +3924,16 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -3942,14 +3942,14 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -4753,49 +4753,49 @@
         <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="U22" t="n">
-        <v>4.23</v>
+        <v>4.22</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="W22" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="X22" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB22" t="n">
         <v>1.08</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG22" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AI22" t="n">
         <v>10.5</v>
@@ -4810,43 +4810,43 @@
         <v>1.68</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AR22" t="n">
         <v>1.9</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AZ22" t="n">
         <v>1.61</v>
@@ -4855,16 +4855,16 @@
         <v>3.04</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BF22" t="n">
         <v>1.09</v>

--- a/jogos_2026-04-02.xlsx
+++ b/jogos_2026-04-02.xlsx
@@ -1738,181 +1738,181 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AN7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>7</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AS7" t="n">
         <v>3.06</v>
       </c>
-      <c r="T7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD7" t="n">
+      <c r="AT7" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AU7" t="n">
         <v>2.54</v>
       </c>
-      <c r="AE7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="AV7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY7" t="n">
         <v>1.12</v>
       </c>
-      <c r="AI7" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,181 +1935,181 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="N8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R8" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AK8" t="n">
-        <v>2.79</v>
+        <v>2.04</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AN8" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.74</v>
+        <v>1.87</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.06</v>
+        <v>2.33</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.43</v>
+        <v>3.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.54</v>
+        <v>3.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,37 +3521,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.16</v>
+        <v>1.68</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.4</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>13</v>
+        <v>5.25</v>
       </c>
       <c r="S16" t="n">
-        <v>1.64</v>
+        <v>2.19</v>
       </c>
       <c r="T16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W16" t="n">
         <v>2.66</v>
       </c>
-      <c r="U16" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.09</v>
-      </c>
       <c r="X16" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.45</v>
+        <v>3.04</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.27</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AI16" t="n">
-        <v>4</v>
+        <v>7.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.34</v>
+        <v>1.9</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.95</v>
+        <v>2.06</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.73</v>
+        <v>3.38</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.88</v>
+        <v>3.12</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.68</v>
+        <v>2.26</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AZ16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.11</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.31</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,171 +3718,171 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>9</v>
+      </c>
+      <c r="N17" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
-        <v>10</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>13</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U17" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z17" t="n">
         <v>5</v>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R17" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="AA17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS17" t="n">
         <v>2.1</v>
       </c>
-      <c r="U17" t="n">
-        <v>5</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.47</v>
-      </c>
       <c r="AT17" t="n">
-        <v>3.38</v>
+        <v>2.73</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.12</v>
+        <v>3.88</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.26</v>
+        <v>2.68</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AZ17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BF17" t="n">
         <v>1.31</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.11</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4121,13 +4121,13 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -4139,24 +4139,24 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>14</v>
+        <v>20.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.71</v>
+        <v>8.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="S19" t="n">
         <v>16</v>
@@ -4318,39 +4318,39 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
         <v>4</v>
@@ -4359,25 +4359,25 @@
         <v>2.32</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="U20" t="n">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="V20" t="n">
         <v>1.38</v>
       </c>
       <c r="W20" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="X20" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
@@ -4386,31 +4386,31 @@
         <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.28</v>
+        <v>3.61</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AI20" t="n">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AL20" t="n">
         <v>1.85</v>
@@ -4419,7 +4419,7 @@
         <v>1.25</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4428,31 +4428,31 @@
         <v>1.25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.19</v>
+        <v>3.28</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AW20" t="n">
         <v>1.81</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AZ20" t="n">
         <v>1.69</v>
@@ -4461,19 +4461,19 @@
         <v>2.56</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4515,108 +4515,108 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Q21" t="n">
         <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="S21" t="n">
         <v>2.23</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U21" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="V21" t="n">
         <v>1.38</v>
       </c>
       <c r="W21" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="X21" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.1</v>
+        <v>6.95</v>
       </c>
       <c r="AA21" t="n">
         <v>1.04</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.33</v>
       </c>
-      <c r="AD21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AI21" t="n">
-        <v>7.35</v>
+        <v>7.18</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AM21" t="n">
         <v>1.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4625,49 +4625,49 @@
         <v>1.16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AU21" t="n">
         <v>4.37</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AZ21" t="n">
         <v>1.25</v>
       </c>
       <c r="BA21" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB21" t="n">
         <v>1.21</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="BD21" t="n">
         <v>3.75</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BF21" t="n">
         <v>1.14</v>
@@ -4712,32 +4712,32 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -4912,54 +4912,54 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R23" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="S23" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="V23" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W23" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="X23" t="n">
         <v>3.1</v>
@@ -4974,34 +4974,34 @@
         <v>1.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
         <v>1.33</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.85</v>
+        <v>3.11</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG23" t="n">
         <v>3.85</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AI23" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AJ23" t="n">
         <v>1.02</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AL23" t="n">
         <v>1.92</v>
@@ -5010,22 +5010,22 @@
         <v>1.6</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.48</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="AT23" t="n">
         <v>2.65</v>
@@ -5034,16 +5034,16 @@
         <v>3.7</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AX23" t="n">
         <v>1.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AZ23" t="n">
         <v>2.27</v>
@@ -5052,19 +5052,19 @@
         <v>1.95</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="BC23" t="n">
         <v>2.25</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BE23" t="n">
         <v>1.53</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.6</v>
+        <v>1.44</v>
       </c>
       <c r="Q25" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U25" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W25" t="n">
         <v>3.3</v>
       </c>
-      <c r="R25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="V25" t="n">
+      <c r="X25" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>1.47</v>
       </c>
-      <c r="W25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AR25" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.55</v>
+        <v>2.92</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.68</v>
+        <v>3.36</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.16</v>
+        <v>1.37</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.34</v>
+        <v>1.88</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.34</v>
+        <v>4.35</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.52</v>
+        <v>3.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="S26" t="n">
-        <v>1.97</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.33</v>
+        <v>1.93</v>
       </c>
       <c r="U26" t="n">
-        <v>5.22</v>
+        <v>2.85</v>
       </c>
       <c r="V26" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="W26" t="n">
-        <v>3.15</v>
+        <v>2.47</v>
       </c>
       <c r="X26" t="n">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.25</v>
+        <v>7.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.8</v>
+        <v>2.83</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.72</v>
+        <v>2.24</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.21</v>
+        <v>1.67</v>
       </c>
       <c r="AG26" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="AI26" t="n">
-        <v>4.75</v>
+        <v>7.3</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AM26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN26" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AQ26" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.3</v>
+        <v>2.16</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.25</v>
+        <v>3.34</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
